--- a/research/traditional_assets/database/data/greece/greece_household_products.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_household_products.xlsx
@@ -1379,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1516,22 +1516,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09771427617851974</v>
+        <v>0.09753440477092701</v>
       </c>
       <c r="C2">
-        <v>835.9573496673992</v>
+        <v>830.4522166930849</v>
       </c>
       <c r="D2">
-        <v>806.1573496673992</v>
+        <v>808.9602166930849</v>
       </c>
       <c r="E2">
-        <v>-110.1</v>
+        <v>-101.792</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.308000000000002</v>
       </c>
       <c r="G2">
         <v>29.8</v>
@@ -1552,28 +1552,28 @@
         <v>61.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4178924000000001</v>
       </c>
       <c r="N2">
-        <v>61.4</v>
+        <v>60.9821076</v>
       </c>
       <c r="O2">
-        <v>13.508</v>
+        <v>13.416063672</v>
       </c>
       <c r="P2">
-        <v>47.892</v>
+        <v>47.566043928</v>
       </c>
       <c r="Q2">
-        <v>57.392</v>
+        <v>57.06604392800001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09771427617851974</v>
+        <v>0.09812329774841111</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.6819479731293349</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>146.9277737522864</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1598,22 +1598,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09753440477092701</v>
+        <v>0.09735453336333426</v>
       </c>
       <c r="C3">
-        <v>830.4522166930849</v>
+        <v>824.9666418683385</v>
       </c>
       <c r="D3">
-        <v>808.9602166930849</v>
+        <v>811.7826418683385</v>
       </c>
       <c r="E3">
-        <v>-101.792</v>
+        <v>-93.48399999999999</v>
       </c>
       <c r="F3">
-        <v>8.308000000000002</v>
+        <v>16.616</v>
       </c>
       <c r="G3">
         <v>29.8</v>
@@ -1634,28 +1634,28 @@
         <v>61.4</v>
       </c>
       <c r="M3">
-        <v>0.4178924000000001</v>
+        <v>0.8357848000000001</v>
       </c>
       <c r="N3">
-        <v>60.9821076</v>
+        <v>60.5642152</v>
       </c>
       <c r="O3">
-        <v>13.416063672</v>
+        <v>13.324127344</v>
       </c>
       <c r="P3">
-        <v>47.566043928</v>
+        <v>47.240087856</v>
       </c>
       <c r="Q3">
-        <v>57.06604392800001</v>
+        <v>56.74008785600001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09812329774841111</v>
+        <v>0.09854066669727986</v>
       </c>
       <c r="T3">
-        <v>0.6819479731293349</v>
+        <v>0.687387689679632</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>146.9277737522864</v>
+        <v>73.46388687614322</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1680,22 +1680,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09735453336333426</v>
+        <v>0.09717466195574151</v>
       </c>
       <c r="C4">
-        <v>824.9666418683385</v>
+        <v>819.500830622359</v>
       </c>
       <c r="D4">
-        <v>811.7826418683385</v>
+        <v>814.624830622359</v>
       </c>
       <c r="E4">
-        <v>-93.48399999999999</v>
+        <v>-85.17599999999999</v>
       </c>
       <c r="F4">
-        <v>16.616</v>
+        <v>24.924</v>
       </c>
       <c r="G4">
         <v>29.8</v>
@@ -1716,28 +1716,28 @@
         <v>61.4</v>
       </c>
       <c r="M4">
-        <v>0.8357848000000001</v>
+        <v>1.2536772</v>
       </c>
       <c r="N4">
-        <v>60.5642152</v>
+        <v>60.1463228</v>
       </c>
       <c r="O4">
-        <v>13.324127344</v>
+        <v>13.232191016</v>
       </c>
       <c r="P4">
-        <v>47.240087856</v>
+        <v>46.914131784</v>
       </c>
       <c r="Q4">
-        <v>56.74008785600001</v>
+        <v>56.41413178400001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09854066669727986</v>
+        <v>0.0989666411914861</v>
       </c>
       <c r="T4">
-        <v>0.687387689679632</v>
+        <v>0.6929395653340591</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.46388687614322</v>
+        <v>48.97592458409549</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1762,22 +1762,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09717466195574151</v>
+        <v>0.09699479054814879</v>
       </c>
       <c r="C5">
-        <v>819.500830622359</v>
+        <v>814.0549912714237</v>
       </c>
       <c r="D5">
-        <v>814.624830622359</v>
+        <v>817.4869912714237</v>
       </c>
       <c r="E5">
-        <v>-85.17599999999999</v>
+        <v>-76.86799999999999</v>
       </c>
       <c r="F5">
-        <v>24.924</v>
+        <v>33.23200000000001</v>
       </c>
       <c r="G5">
         <v>29.8</v>
@@ -1798,28 +1798,28 @@
         <v>61.4</v>
       </c>
       <c r="M5">
-        <v>1.2536772</v>
+        <v>1.6715696</v>
       </c>
       <c r="N5">
-        <v>60.1463228</v>
+        <v>59.7284304</v>
       </c>
       <c r="O5">
-        <v>13.232191016</v>
+        <v>13.140254688</v>
       </c>
       <c r="P5">
-        <v>46.914131784</v>
+        <v>46.588175712</v>
       </c>
       <c r="Q5">
-        <v>56.41413178400001</v>
+        <v>56.08817571200001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0989666411914861</v>
+        <v>0.09940149015432165</v>
       </c>
       <c r="T5">
-        <v>0.6929395653340591</v>
+        <v>0.6986071050646201</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.97592458409549</v>
+        <v>36.73194343807162</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1844,22 +1844,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09699479054814879</v>
+        <v>0.09681491914055602</v>
       </c>
       <c r="C6">
-        <v>814.0549912714237</v>
+        <v>808.6293350697866</v>
       </c>
       <c r="D6">
-        <v>817.4869912714237</v>
+        <v>820.3693350697866</v>
       </c>
       <c r="E6">
-        <v>-76.86799999999999</v>
+        <v>-68.55999999999999</v>
       </c>
       <c r="F6">
-        <v>33.23200000000001</v>
+        <v>41.54000000000001</v>
       </c>
       <c r="G6">
         <v>29.8</v>
@@ -1880,28 +1880,28 @@
         <v>61.4</v>
       </c>
       <c r="M6">
-        <v>1.6715696</v>
+        <v>2.089462</v>
       </c>
       <c r="N6">
-        <v>59.7284304</v>
+        <v>59.310538</v>
       </c>
       <c r="O6">
-        <v>13.140254688</v>
+        <v>13.04831836</v>
       </c>
       <c r="P6">
-        <v>46.588175712</v>
+        <v>46.26221964</v>
       </c>
       <c r="Q6">
-        <v>56.08817571200001</v>
+        <v>55.76221964</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09940149015432165</v>
+        <v>0.09984549383216425</v>
       </c>
       <c r="T6">
-        <v>0.6986071050646201</v>
+        <v>0.7043939614210876</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.73194343807162</v>
+        <v>29.38555475045729</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1926,22 +1926,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09681491914055602</v>
+        <v>0.09663504773296328</v>
       </c>
       <c r="C7">
-        <v>808.6293350697866</v>
+        <v>803.2240762616523</v>
       </c>
       <c r="D7">
-        <v>820.3693350697866</v>
+        <v>823.2720762616523</v>
       </c>
       <c r="E7">
-        <v>-68.55999999999999</v>
+        <v>-60.25199999999999</v>
       </c>
       <c r="F7">
-        <v>41.54000000000001</v>
+        <v>49.84800000000001</v>
       </c>
       <c r="G7">
         <v>29.8</v>
@@ -1962,28 +1962,28 @@
         <v>61.4</v>
       </c>
       <c r="M7">
-        <v>2.089462</v>
+        <v>2.5073544</v>
       </c>
       <c r="N7">
-        <v>59.310538</v>
+        <v>58.8926456</v>
       </c>
       <c r="O7">
-        <v>13.04831836</v>
+        <v>12.956382032</v>
       </c>
       <c r="P7">
-        <v>46.26221964</v>
+        <v>45.936263568</v>
       </c>
       <c r="Q7">
-        <v>55.76221964</v>
+        <v>55.43626356800001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09984549383216425</v>
+        <v>0.1002989443967695</v>
       </c>
       <c r="T7">
-        <v>0.7043939614210876</v>
+        <v>0.7103039423808841</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.38555475045729</v>
+        <v>24.48796229204774</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2008,22 +2008,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09663504773296328</v>
+        <v>0.09645517632537054</v>
       </c>
       <c r="C8">
-        <v>803.2240762616523</v>
+        <v>797.8394321342645</v>
       </c>
       <c r="D8">
-        <v>823.2720762616523</v>
+        <v>826.1954321342645</v>
       </c>
       <c r="E8">
-        <v>-60.252</v>
+        <v>-51.944</v>
       </c>
       <c r="F8">
-        <v>49.848</v>
+        <v>58.156</v>
       </c>
       <c r="G8">
         <v>29.8</v>
@@ -2044,28 +2044,28 @@
         <v>61.4</v>
       </c>
       <c r="M8">
-        <v>2.5073544</v>
+        <v>2.9252468</v>
       </c>
       <c r="N8">
-        <v>58.8926456</v>
+        <v>58.4747532</v>
       </c>
       <c r="O8">
-        <v>12.956382032</v>
+        <v>12.864445704</v>
       </c>
       <c r="P8">
-        <v>45.936263568</v>
+        <v>45.610307496</v>
       </c>
       <c r="Q8">
-        <v>55.43626356800001</v>
+        <v>55.11030749600001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1002989443967695</v>
+        <v>0.1007621465864199</v>
       </c>
       <c r="T8">
-        <v>0.7103039423808841</v>
+        <v>0.7163410197054074</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.48796229204775</v>
+        <v>20.98968196461236</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2090,22 +2090,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09645517632537054</v>
+        <v>0.0962753049177778</v>
       </c>
       <c r="C9">
-        <v>797.8394321342644</v>
+        <v>792.4756230721251</v>
       </c>
       <c r="D9">
-        <v>826.1954321342645</v>
+        <v>829.1396230721252</v>
       </c>
       <c r="E9">
-        <v>-51.94399999999998</v>
+        <v>-43.63599999999998</v>
       </c>
       <c r="F9">
-        <v>58.15600000000001</v>
+        <v>66.46400000000001</v>
       </c>
       <c r="G9">
         <v>29.8</v>
@@ -2126,28 +2126,28 @@
         <v>61.4</v>
       </c>
       <c r="M9">
-        <v>2.9252468</v>
+        <v>3.3431392</v>
       </c>
       <c r="N9">
-        <v>58.47475319999999</v>
+        <v>58.0568608</v>
       </c>
       <c r="O9">
-        <v>12.864445704</v>
+        <v>12.772509376</v>
       </c>
       <c r="P9">
-        <v>45.610307496</v>
+        <v>45.28435142399999</v>
       </c>
       <c r="Q9">
-        <v>55.110307496</v>
+        <v>54.784351424</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1007621465864199</v>
+        <v>0.1012354183888889</v>
       </c>
       <c r="T9">
-        <v>0.7163410197054075</v>
+        <v>0.7225093378413335</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.98968196461235</v>
+        <v>18.36597171903581</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2172,22 +2172,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0962753049177778</v>
+        <v>0.09609543351018507</v>
       </c>
       <c r="C10">
-        <v>792.4756230721251</v>
+        <v>787.1328726123779</v>
       </c>
       <c r="D10">
-        <v>829.1396230721252</v>
+        <v>832.104872612378</v>
       </c>
       <c r="E10">
-        <v>-43.63599999999998</v>
+        <v>-35.32799999999999</v>
       </c>
       <c r="F10">
-        <v>66.46400000000001</v>
+        <v>74.77200000000001</v>
       </c>
       <c r="G10">
         <v>29.8</v>
@@ -2208,28 +2208,28 @@
         <v>61.4</v>
       </c>
       <c r="M10">
-        <v>3.3431392</v>
+        <v>3.7610316</v>
       </c>
       <c r="N10">
-        <v>58.0568608</v>
+        <v>57.6389684</v>
       </c>
       <c r="O10">
-        <v>12.772509376</v>
+        <v>12.680573048</v>
       </c>
       <c r="P10">
-        <v>45.28435142399999</v>
+        <v>44.958395352</v>
       </c>
       <c r="Q10">
-        <v>54.784351424</v>
+        <v>54.458395352</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1012354183888889</v>
+        <v>0.1017190917694341</v>
       </c>
       <c r="T10">
-        <v>0.7225093378413335</v>
+        <v>0.7288132234088185</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.36597171903581</v>
+        <v>16.3253081946985</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2254,22 +2254,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09609543351018507</v>
+        <v>0.09591556210259231</v>
       </c>
       <c r="C11">
-        <v>787.1328726123779</v>
+        <v>781.8114075013849</v>
       </c>
       <c r="D11">
-        <v>832.104872612378</v>
+        <v>835.091407501385</v>
       </c>
       <c r="E11">
-        <v>-35.32799999999999</v>
+        <v>-27.02</v>
       </c>
       <c r="F11">
-        <v>74.77200000000001</v>
+        <v>83.08</v>
       </c>
       <c r="G11">
         <v>29.8</v>
@@ -2290,28 +2290,28 @@
         <v>61.4</v>
       </c>
       <c r="M11">
-        <v>3.7610316</v>
+        <v>4.178923999999999</v>
       </c>
       <c r="N11">
-        <v>57.6389684</v>
+        <v>57.221076</v>
       </c>
       <c r="O11">
-        <v>12.680573048</v>
+        <v>12.58863672</v>
       </c>
       <c r="P11">
-        <v>44.958395352</v>
+        <v>44.63243928</v>
       </c>
       <c r="Q11">
-        <v>54.458395352</v>
+        <v>54.13243928000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1017190917694341</v>
+        <v>0.1022135134473248</v>
       </c>
       <c r="T11">
-        <v>0.7288132234088185</v>
+        <v>0.7352571953222474</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.3253081946985</v>
+        <v>14.69277737522865</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2336,22 +2336,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09591556210259231</v>
+        <v>0.09573569069499958</v>
       </c>
       <c r="C12">
-        <v>781.8114075013849</v>
+        <v>776.5114577525233</v>
       </c>
       <c r="D12">
-        <v>835.091407501385</v>
+        <v>838.0994577525233</v>
       </c>
       <c r="E12">
-        <v>-27.01999999999998</v>
+        <v>-18.71199999999999</v>
       </c>
       <c r="F12">
-        <v>83.08000000000001</v>
+        <v>91.38800000000001</v>
       </c>
       <c r="G12">
         <v>29.8</v>
@@ -2372,28 +2372,28 @@
         <v>61.4</v>
       </c>
       <c r="M12">
-        <v>4.178924</v>
+        <v>4.5968164</v>
       </c>
       <c r="N12">
-        <v>57.221076</v>
+        <v>56.8031836</v>
       </c>
       <c r="O12">
-        <v>12.58863672</v>
+        <v>12.496700392</v>
       </c>
       <c r="P12">
-        <v>44.63243928</v>
+        <v>44.306483208</v>
       </c>
       <c r="Q12">
-        <v>54.13243928000001</v>
+        <v>53.806483208</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1022135134473248</v>
+        <v>0.1027190457247186</v>
       </c>
       <c r="T12">
-        <v>0.7352571953222474</v>
+        <v>0.7418459755932817</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.69277737522865</v>
+        <v>13.35707034111695</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2418,22 +2418,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09573569069499958</v>
+        <v>0.09569621928740682</v>
       </c>
       <c r="C13">
-        <v>776.5114577525233</v>
+        <v>768.8664531812886</v>
       </c>
       <c r="D13">
-        <v>838.0994577525233</v>
+        <v>838.7624531812887</v>
       </c>
       <c r="E13">
-        <v>-18.71199999999999</v>
+        <v>-10.404</v>
       </c>
       <c r="F13">
-        <v>91.38800000000001</v>
+        <v>99.696</v>
       </c>
       <c r="G13">
         <v>29.8</v>
@@ -2454,45 +2454,45 @@
         <v>61.4</v>
       </c>
       <c r="M13">
-        <v>4.5968164</v>
+        <v>5.1642528</v>
       </c>
       <c r="N13">
-        <v>56.8031836</v>
+        <v>56.2357472</v>
       </c>
       <c r="O13">
-        <v>12.496700392</v>
+        <v>12.371864384</v>
       </c>
       <c r="P13">
-        <v>44.306483208</v>
+        <v>43.863882816</v>
       </c>
       <c r="Q13">
-        <v>53.806483208</v>
+        <v>53.36388281600001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1027190457247186</v>
+        <v>0.1032360673720532</v>
       </c>
       <c r="T13">
-        <v>0.7418459755932817</v>
+        <v>0.7485845008704756</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.35707034111695</v>
+        <v>11.88942570743245</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2500,22 +2500,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09569621928740682</v>
+        <v>0.09552804787981407</v>
       </c>
       <c r="C14">
-        <v>768.8664531812886</v>
+        <v>763.3949985194117</v>
       </c>
       <c r="D14">
-        <v>838.7624531812887</v>
+        <v>841.5989985194118</v>
       </c>
       <c r="E14">
-        <v>-10.404</v>
+        <v>-2.095999999999975</v>
       </c>
       <c r="F14">
-        <v>99.696</v>
+        <v>108.004</v>
       </c>
       <c r="G14">
         <v>29.8</v>
@@ -2536,28 +2536,28 @@
         <v>61.4</v>
       </c>
       <c r="M14">
-        <v>5.1642528</v>
+        <v>5.5946072</v>
       </c>
       <c r="N14">
-        <v>56.2357472</v>
+        <v>55.8053928</v>
       </c>
       <c r="O14">
-        <v>12.371864384</v>
+        <v>12.277186416</v>
       </c>
       <c r="P14">
-        <v>43.863882816</v>
+        <v>43.528206384</v>
       </c>
       <c r="Q14">
-        <v>53.36388281600001</v>
+        <v>53.02820638400001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1032360673720532</v>
+        <v>0.1037649745744989</v>
       </c>
       <c r="T14">
-        <v>0.7485845008704756</v>
+        <v>0.7554779347747315</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.88942570743245</v>
+        <v>10.97485449916841</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2582,22 +2582,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09552804787981407</v>
+        <v>0.09535987647222134</v>
       </c>
       <c r="C15">
-        <v>763.3949985194117</v>
+        <v>757.9427943422477</v>
       </c>
       <c r="D15">
-        <v>841.5989985194118</v>
+        <v>844.4547943422477</v>
       </c>
       <c r="E15">
-        <v>-2.095999999999975</v>
+        <v>6.212000000000032</v>
       </c>
       <c r="F15">
-        <v>108.004</v>
+        <v>116.312</v>
       </c>
       <c r="G15">
         <v>29.8</v>
@@ -2618,28 +2618,28 @@
         <v>61.4</v>
       </c>
       <c r="M15">
-        <v>5.5946072</v>
+        <v>6.024961600000001</v>
       </c>
       <c r="N15">
-        <v>55.8053928</v>
+        <v>55.37503839999999</v>
       </c>
       <c r="O15">
-        <v>12.277186416</v>
+        <v>12.182508448</v>
       </c>
       <c r="P15">
-        <v>43.528206384</v>
+        <v>43.19252995199999</v>
       </c>
       <c r="Q15">
-        <v>53.02820638400001</v>
+        <v>52.692529952</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1037649745744989</v>
+        <v>0.1043061819444434</v>
       </c>
       <c r="T15">
-        <v>0.7554779347747315</v>
+        <v>0.7625316810953655</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.97485449916841</v>
+        <v>10.19093632065638</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2664,22 +2664,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09535987647222134</v>
+        <v>0.0953906050646286</v>
       </c>
       <c r="C16">
-        <v>757.9427943422477</v>
+        <v>749.1115317777383</v>
       </c>
       <c r="D16">
-        <v>844.4547943422477</v>
+        <v>843.9315317777383</v>
       </c>
       <c r="E16">
-        <v>6.212000000000032</v>
+        <v>14.52000000000004</v>
       </c>
       <c r="F16">
-        <v>116.312</v>
+        <v>124.62</v>
       </c>
       <c r="G16">
         <v>29.8</v>
@@ -2700,45 +2700,45 @@
         <v>61.4</v>
       </c>
       <c r="M16">
-        <v>6.024961600000001</v>
+        <v>6.667170000000001</v>
       </c>
       <c r="N16">
-        <v>55.37503839999999</v>
+        <v>54.73283</v>
       </c>
       <c r="O16">
-        <v>12.182508448</v>
+        <v>12.0412226</v>
       </c>
       <c r="P16">
-        <v>43.19252995199999</v>
+        <v>42.6916074</v>
       </c>
       <c r="Q16">
-        <v>52.692529952</v>
+        <v>52.19160740000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1043061819444434</v>
+        <v>0.1048601236054454</v>
       </c>
       <c r="T16">
-        <v>0.7625316810953655</v>
+        <v>0.7697513979176615</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.19093632065638</v>
+        <v>9.209304697495337</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2746,22 +2746,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0953906050646286</v>
+        <v>0.09523569365703584</v>
       </c>
       <c r="C17">
-        <v>749.1115317777383</v>
+        <v>743.4480708107411</v>
       </c>
       <c r="D17">
-        <v>843.9315317777383</v>
+        <v>846.5760708107412</v>
       </c>
       <c r="E17">
-        <v>14.52000000000001</v>
+        <v>22.82800000000003</v>
       </c>
       <c r="F17">
-        <v>124.62</v>
+        <v>132.928</v>
       </c>
       <c r="G17">
         <v>29.8</v>
@@ -2782,28 +2782,28 @@
         <v>61.4</v>
       </c>
       <c r="M17">
-        <v>6.66717</v>
+        <v>7.111648000000002</v>
       </c>
       <c r="N17">
-        <v>54.73283</v>
+        <v>54.288352</v>
       </c>
       <c r="O17">
-        <v>12.0412226</v>
+        <v>11.94343744</v>
       </c>
       <c r="P17">
-        <v>42.6916074</v>
+        <v>42.34491456</v>
       </c>
       <c r="Q17">
-        <v>52.19160740000001</v>
+        <v>51.84491456000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1048601236054454</v>
+        <v>0.1054272543536141</v>
       </c>
       <c r="T17">
-        <v>0.7697513979176615</v>
+        <v>0.7771430127595359</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.209304697495339</v>
+        <v>8.633723153901879</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2828,22 +2828,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09523569365703584</v>
+        <v>0.09508078224944312</v>
       </c>
       <c r="C18">
-        <v>743.4480708107411</v>
+        <v>737.8012357674943</v>
       </c>
       <c r="D18">
-        <v>846.5760708107412</v>
+        <v>849.2372357674943</v>
       </c>
       <c r="E18">
-        <v>22.82800000000003</v>
+        <v>31.13600000000002</v>
       </c>
       <c r="F18">
-        <v>132.928</v>
+        <v>141.236</v>
       </c>
       <c r="G18">
         <v>29.8</v>
@@ -2864,28 +2864,28 @@
         <v>61.4</v>
       </c>
       <c r="M18">
-        <v>7.111648000000002</v>
+        <v>7.556126000000001</v>
       </c>
       <c r="N18">
-        <v>54.288352</v>
+        <v>53.843874</v>
       </c>
       <c r="O18">
-        <v>11.94343744</v>
+        <v>11.84565228</v>
       </c>
       <c r="P18">
-        <v>42.34491456</v>
+        <v>41.99822172</v>
       </c>
       <c r="Q18">
-        <v>51.84491456000001</v>
+        <v>51.49822172000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1054272543536141</v>
+        <v>0.1060080509029435</v>
       </c>
       <c r="T18">
-        <v>0.7771430127595359</v>
+        <v>0.7847127388024193</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.633723153901879</v>
+        <v>8.125857086025299</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2910,22 +2910,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09508078224944312</v>
+        <v>0.09492587084185036</v>
       </c>
       <c r="C19">
-        <v>737.8012357674943</v>
+        <v>732.1711839304173</v>
       </c>
       <c r="D19">
-        <v>849.2372357674943</v>
+        <v>851.9151839304174</v>
       </c>
       <c r="E19">
-        <v>31.13600000000002</v>
+        <v>39.44400000000005</v>
       </c>
       <c r="F19">
-        <v>141.236</v>
+        <v>149.544</v>
       </c>
       <c r="G19">
         <v>29.8</v>
@@ -2946,28 +2946,28 @@
         <v>61.4</v>
       </c>
       <c r="M19">
-        <v>7.556126000000001</v>
+        <v>8.000604000000003</v>
       </c>
       <c r="N19">
-        <v>53.843874</v>
+        <v>53.399396</v>
       </c>
       <c r="O19">
-        <v>11.84565228</v>
+        <v>11.74786712</v>
       </c>
       <c r="P19">
-        <v>41.99822172</v>
+        <v>41.65152888</v>
       </c>
       <c r="Q19">
-        <v>51.49822172000001</v>
+        <v>51.15152888000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1060080509029435</v>
+        <v>0.1066030132217687</v>
       </c>
       <c r="T19">
-        <v>0.7847127388024193</v>
+        <v>0.7924670923097634</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.125857086025299</v>
+        <v>7.674420581246113</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2992,22 +2992,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09492587084185038</v>
+        <v>0.09488951943425764</v>
       </c>
       <c r="C20">
-        <v>732.1711839304171</v>
+        <v>724.4940378569253</v>
       </c>
       <c r="D20">
-        <v>851.9151839304171</v>
+        <v>852.5460378569253</v>
       </c>
       <c r="E20">
-        <v>39.44400000000002</v>
+        <v>47.75200000000001</v>
       </c>
       <c r="F20">
-        <v>149.544</v>
+        <v>157.852</v>
       </c>
       <c r="G20">
         <v>29.8</v>
@@ -3028,45 +3028,45 @@
         <v>61.4</v>
       </c>
       <c r="M20">
-        <v>8.000604000000001</v>
+        <v>8.5713636</v>
       </c>
       <c r="N20">
-        <v>53.399396</v>
+        <v>52.8286364</v>
       </c>
       <c r="O20">
-        <v>11.74786712</v>
+        <v>11.622300008</v>
       </c>
       <c r="P20">
-        <v>41.65152888</v>
+        <v>41.206336392</v>
       </c>
       <c r="Q20">
-        <v>51.15152888000001</v>
+        <v>50.706336392</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1066030132217687</v>
+        <v>0.1072126659682193</v>
       </c>
       <c r="T20">
-        <v>0.7924670923097633</v>
+        <v>0.8004129113358072</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.674420581246115</v>
+        <v>7.163387631811583</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3074,22 +3074,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09488951943425764</v>
+        <v>0.09474084802666488</v>
       </c>
       <c r="C21">
-        <v>724.4940378569253</v>
+        <v>718.7758830393534</v>
       </c>
       <c r="D21">
-        <v>852.5460378569253</v>
+        <v>855.1358830393535</v>
       </c>
       <c r="E21">
-        <v>47.75200000000001</v>
+        <v>56.06000000000003</v>
       </c>
       <c r="F21">
-        <v>157.852</v>
+        <v>166.16</v>
       </c>
       <c r="G21">
         <v>29.8</v>
@@ -3110,28 +3110,28 @@
         <v>61.4</v>
       </c>
       <c r="M21">
-        <v>8.5713636</v>
+        <v>9.022488000000001</v>
       </c>
       <c r="N21">
-        <v>52.8286364</v>
+        <v>52.377512</v>
       </c>
       <c r="O21">
-        <v>11.622300008</v>
+        <v>11.52305264</v>
       </c>
       <c r="P21">
-        <v>41.206336392</v>
+        <v>40.85445935999999</v>
       </c>
       <c r="Q21">
-        <v>50.706336392</v>
+        <v>50.35445936</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1072126659682193</v>
+        <v>0.1078375600333311</v>
       </c>
       <c r="T21">
-        <v>0.8004129113358072</v>
+        <v>0.8085573758375022</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.163387631811583</v>
+        <v>6.805218250221002</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3156,22 +3156,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09474084802666488</v>
+        <v>0.09459217661907214</v>
       </c>
       <c r="C22">
-        <v>718.7758830393534</v>
+        <v>713.0735109129998</v>
       </c>
       <c r="D22">
-        <v>855.1358830393535</v>
+        <v>857.7415109129998</v>
       </c>
       <c r="E22">
-        <v>56.06000000000003</v>
+        <v>64.36800000000002</v>
       </c>
       <c r="F22">
-        <v>166.16</v>
+        <v>174.468</v>
       </c>
       <c r="G22">
         <v>29.8</v>
@@ -3192,28 +3192,28 @@
         <v>61.4</v>
       </c>
       <c r="M22">
-        <v>9.022488000000001</v>
+        <v>9.4736124</v>
       </c>
       <c r="N22">
-        <v>52.377512</v>
+        <v>51.9263876</v>
       </c>
       <c r="O22">
-        <v>11.52305264</v>
+        <v>11.423805272</v>
       </c>
       <c r="P22">
-        <v>40.85445935999999</v>
+        <v>40.502582328</v>
       </c>
       <c r="Q22">
-        <v>50.35445936</v>
+        <v>50.00258232800001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1078375600333311</v>
+        <v>0.1084782742013571</v>
       </c>
       <c r="T22">
-        <v>0.8085573758375022</v>
+        <v>0.8169080293139237</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.805218250221002</v>
+        <v>6.481160238305717</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3238,22 +3238,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09459217661907214</v>
+        <v>0.09444350521147939</v>
       </c>
       <c r="C23">
-        <v>713.0735109129998</v>
+        <v>707.3870661899841</v>
       </c>
       <c r="D23">
-        <v>857.7415109129998</v>
+        <v>860.3630661899842</v>
       </c>
       <c r="E23">
-        <v>64.36800000000002</v>
+        <v>72.67600000000002</v>
       </c>
       <c r="F23">
-        <v>174.468</v>
+        <v>182.776</v>
       </c>
       <c r="G23">
         <v>29.8</v>
@@ -3274,28 +3274,28 @@
         <v>61.4</v>
       </c>
       <c r="M23">
-        <v>9.4736124</v>
+        <v>9.924736800000002</v>
       </c>
       <c r="N23">
-        <v>51.9263876</v>
+        <v>51.4752632</v>
       </c>
       <c r="O23">
-        <v>11.423805272</v>
+        <v>11.324557904</v>
       </c>
       <c r="P23">
-        <v>40.502582328</v>
+        <v>40.150705296</v>
       </c>
       <c r="Q23">
-        <v>50.00258232800001</v>
+        <v>49.65070529600001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1084782742013571</v>
+        <v>0.1091354169377941</v>
       </c>
       <c r="T23">
-        <v>0.8169080293139235</v>
+        <v>0.8254728021102532</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.481160238305717</v>
+        <v>6.186562045655457</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3320,22 +3320,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09444350521147939</v>
+        <v>0.09447423380388664</v>
       </c>
       <c r="C24">
-        <v>707.3870661899841</v>
+        <v>698.5359092891538</v>
       </c>
       <c r="D24">
-        <v>860.3630661899842</v>
+        <v>859.8199092891539</v>
       </c>
       <c r="E24">
-        <v>72.67600000000002</v>
+        <v>80.98400000000004</v>
       </c>
       <c r="F24">
-        <v>182.776</v>
+        <v>191.084</v>
       </c>
       <c r="G24">
         <v>29.8</v>
@@ -3356,45 +3356,45 @@
         <v>61.4</v>
       </c>
       <c r="M24">
-        <v>9.924736800000002</v>
+        <v>10.5669452</v>
       </c>
       <c r="N24">
-        <v>51.4752632</v>
+        <v>50.8330548</v>
       </c>
       <c r="O24">
-        <v>11.324557904</v>
+        <v>11.183272056</v>
       </c>
       <c r="P24">
-        <v>40.150705296</v>
+        <v>39.649782744</v>
       </c>
       <c r="Q24">
-        <v>49.65070529600001</v>
+        <v>49.14978274400001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1091354169377941</v>
+        <v>0.1098096283167359</v>
       </c>
       <c r="T24">
-        <v>0.8254728021102532</v>
+        <v>0.8342600365376565</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.186562045655457</v>
+        <v>5.810572387561922</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3402,22 +3402,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09447423380388664</v>
+        <v>0.0943333623962939</v>
       </c>
       <c r="C25">
-        <v>698.5359092891538</v>
+        <v>692.7235954505369</v>
       </c>
       <c r="D25">
-        <v>859.8199092891539</v>
+        <v>862.315595450537</v>
       </c>
       <c r="E25">
-        <v>80.98400000000004</v>
+        <v>89.29200000000003</v>
       </c>
       <c r="F25">
-        <v>191.084</v>
+        <v>199.392</v>
       </c>
       <c r="G25">
         <v>29.8</v>
@@ -3438,28 +3438,28 @@
         <v>61.4</v>
       </c>
       <c r="M25">
-        <v>10.5669452</v>
+        <v>11.0263776</v>
       </c>
       <c r="N25">
-        <v>50.8330548</v>
+        <v>50.3736224</v>
       </c>
       <c r="O25">
-        <v>11.183272056</v>
+        <v>11.082196928</v>
       </c>
       <c r="P25">
-        <v>39.649782744</v>
+        <v>39.291425472</v>
       </c>
       <c r="Q25">
-        <v>49.14978274400001</v>
+        <v>48.79142547200001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1098096283167359</v>
+        <v>0.1105015821003867</v>
       </c>
       <c r="T25">
-        <v>0.8342600365376565</v>
+        <v>0.843278513976307</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.810572387561922</v>
+        <v>5.568465204746841</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3484,22 +3484,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0943333623962939</v>
+        <v>0.09419249098870117</v>
       </c>
       <c r="C26">
-        <v>692.723595450537</v>
+        <v>686.9258115861073</v>
       </c>
       <c r="D26">
-        <v>862.315595450537</v>
+        <v>864.8258115861074</v>
       </c>
       <c r="E26">
-        <v>89.292</v>
+        <v>97.60000000000002</v>
       </c>
       <c r="F26">
-        <v>199.392</v>
+        <v>207.7</v>
       </c>
       <c r="G26">
         <v>29.8</v>
@@ -3520,28 +3520,28 @@
         <v>61.4</v>
       </c>
       <c r="M26">
-        <v>11.0263776</v>
+        <v>11.48581</v>
       </c>
       <c r="N26">
-        <v>50.3736224</v>
+        <v>49.91419</v>
       </c>
       <c r="O26">
-        <v>11.082196928</v>
+        <v>10.9811218</v>
       </c>
       <c r="P26">
-        <v>39.291425472</v>
+        <v>38.93306819999999</v>
       </c>
       <c r="Q26">
-        <v>48.79142547200001</v>
+        <v>48.4330682</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1105015821003867</v>
+        <v>0.1112119879849349</v>
       </c>
       <c r="T26">
-        <v>0.843278513976307</v>
+        <v>0.852537484146655</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.568465204746843</v>
+        <v>5.345726596556968</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3566,22 +3566,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09419249098870117</v>
+        <v>0.09405161958110841</v>
       </c>
       <c r="C27">
-        <v>686.9258115861073</v>
+        <v>681.1426849573709</v>
       </c>
       <c r="D27">
-        <v>864.8258115861074</v>
+        <v>867.350684957371</v>
       </c>
       <c r="E27">
-        <v>97.60000000000002</v>
+        <v>105.908</v>
       </c>
       <c r="F27">
-        <v>207.7</v>
+        <v>216.008</v>
       </c>
       <c r="G27">
         <v>29.8</v>
@@ -3602,28 +3602,28 @@
         <v>61.4</v>
       </c>
       <c r="M27">
-        <v>11.48581</v>
+        <v>11.9452424</v>
       </c>
       <c r="N27">
-        <v>49.91419</v>
+        <v>49.45475759999999</v>
       </c>
       <c r="O27">
-        <v>10.9811218</v>
+        <v>10.880046672</v>
       </c>
       <c r="P27">
-        <v>38.93306819999999</v>
+        <v>38.57471092799999</v>
       </c>
       <c r="Q27">
-        <v>48.4330682</v>
+        <v>48.074710928</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1112119879849349</v>
+        <v>0.1119415940285249</v>
       </c>
       <c r="T27">
-        <v>0.852537484146655</v>
+        <v>0.8620466967540394</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.345726596556968</v>
+        <v>5.140121727458622</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3648,22 +3648,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09405161958110841</v>
+        <v>0.09391074817351568</v>
       </c>
       <c r="C28">
-        <v>681.1426849573709</v>
+        <v>675.3743443163526</v>
       </c>
       <c r="D28">
-        <v>867.350684957371</v>
+        <v>869.8903443163526</v>
       </c>
       <c r="E28">
-        <v>105.908</v>
+        <v>114.216</v>
       </c>
       <c r="F28">
-        <v>216.008</v>
+        <v>224.316</v>
       </c>
       <c r="G28">
         <v>29.8</v>
@@ -3684,28 +3684,28 @@
         <v>61.4</v>
       </c>
       <c r="M28">
-        <v>11.9452424</v>
+        <v>12.4046748</v>
       </c>
       <c r="N28">
-        <v>49.45475759999999</v>
+        <v>48.9953252</v>
       </c>
       <c r="O28">
-        <v>10.880046672</v>
+        <v>10.778971544</v>
       </c>
       <c r="P28">
-        <v>38.57471092799999</v>
+        <v>38.216353656</v>
       </c>
       <c r="Q28">
-        <v>48.074710928</v>
+        <v>47.716353656</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1119415940285249</v>
+        <v>0.1126911892787886</v>
       </c>
       <c r="T28">
-        <v>0.8620466967540394</v>
+        <v>0.8718164357342288</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.140121727458622</v>
+        <v>4.949746848663859</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3730,22 +3730,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09391074817351568</v>
+        <v>0.09376987676592294</v>
       </c>
       <c r="C29">
-        <v>675.3743443163526</v>
+        <v>669.6209199274832</v>
       </c>
       <c r="D29">
-        <v>869.8903443163526</v>
+        <v>872.4449199274833</v>
       </c>
       <c r="E29">
-        <v>114.216</v>
+        <v>122.5240000000001</v>
       </c>
       <c r="F29">
-        <v>224.316</v>
+        <v>232.6240000000001</v>
       </c>
       <c r="G29">
         <v>29.8</v>
@@ -3766,28 +3766,28 @@
         <v>61.4</v>
       </c>
       <c r="M29">
-        <v>12.4046748</v>
+        <v>12.8641072</v>
       </c>
       <c r="N29">
-        <v>48.9953252</v>
+        <v>48.5358928</v>
       </c>
       <c r="O29">
-        <v>10.778971544</v>
+        <v>10.677896416</v>
       </c>
       <c r="P29">
-        <v>38.216353656</v>
+        <v>37.857996384</v>
       </c>
       <c r="Q29">
-        <v>47.716353656</v>
+        <v>47.35799638400001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1126911892787886</v>
+        <v>0.1134616066193374</v>
       </c>
       <c r="T29">
-        <v>0.8718164357342288</v>
+        <v>0.881857556352757</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.949746848663859</v>
+        <v>4.772970175497292</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3812,22 +3812,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09376987676592294</v>
+        <v>0.09362900535833021</v>
       </c>
       <c r="C30">
-        <v>669.6209199274832</v>
+        <v>663.8825435898725</v>
       </c>
       <c r="D30">
-        <v>872.4449199274833</v>
+        <v>875.0145435898726</v>
       </c>
       <c r="E30">
-        <v>122.5240000000001</v>
+        <v>130.8320000000001</v>
       </c>
       <c r="F30">
-        <v>232.6240000000001</v>
+        <v>240.932</v>
       </c>
       <c r="G30">
         <v>29.8</v>
@@ -3848,28 +3848,28 @@
         <v>61.4</v>
       </c>
       <c r="M30">
-        <v>12.8641072</v>
+        <v>13.3235396</v>
       </c>
       <c r="N30">
-        <v>48.5358928</v>
+        <v>48.07646039999999</v>
       </c>
       <c r="O30">
-        <v>10.677896416</v>
+        <v>10.576821288</v>
       </c>
       <c r="P30">
-        <v>37.857996384</v>
+        <v>37.499639112</v>
       </c>
       <c r="Q30">
-        <v>47.35799638400001</v>
+        <v>46.999639112</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1134616066193374</v>
+        <v>0.1142537258568031</v>
       </c>
       <c r="T30">
-        <v>0.881857556352757</v>
+        <v>0.8921815254394125</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.772970175497292</v>
+        <v>4.608384997031868</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3894,22 +3894,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0936290053583302</v>
+        <v>0.09407313395073745</v>
       </c>
       <c r="C31">
-        <v>663.8825435898726</v>
+        <v>647.5241241168584</v>
       </c>
       <c r="D31">
-        <v>875.0145435898727</v>
+        <v>866.9641241168584</v>
       </c>
       <c r="E31">
-        <v>130.832</v>
+        <v>139.14</v>
       </c>
       <c r="F31">
-        <v>240.932</v>
+        <v>249.24</v>
       </c>
       <c r="G31">
         <v>29.8</v>
@@ -3930,45 +3930,45 @@
         <v>61.4</v>
       </c>
       <c r="M31">
-        <v>13.3235396</v>
+        <v>14.406072</v>
       </c>
       <c r="N31">
-        <v>48.07646039999999</v>
+        <v>46.993928</v>
       </c>
       <c r="O31">
-        <v>10.576821288</v>
+        <v>10.33866416</v>
       </c>
       <c r="P31">
-        <v>37.499639112</v>
+        <v>36.65526384</v>
       </c>
       <c r="Q31">
-        <v>46.999639112</v>
+        <v>46.15526384</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1142537258568031</v>
+        <v>0.1150684770724821</v>
       </c>
       <c r="T31">
-        <v>0.8921815254394125</v>
+        <v>0.9028004650714011</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.60838499703187</v>
+        <v>4.262091706885818</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3976,22 +3976,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09407313395073745</v>
+        <v>0.09395176254314469</v>
       </c>
       <c r="C32">
-        <v>647.5241241168584</v>
+        <v>641.4013952371462</v>
       </c>
       <c r="D32">
-        <v>866.9641241168584</v>
+        <v>869.1493952371462</v>
       </c>
       <c r="E32">
-        <v>139.14</v>
+        <v>147.448</v>
       </c>
       <c r="F32">
-        <v>249.24</v>
+        <v>257.548</v>
       </c>
       <c r="G32">
         <v>29.8</v>
@@ -4012,28 +4012,28 @@
         <v>61.4</v>
       </c>
       <c r="M32">
-        <v>14.406072</v>
+        <v>14.8862744</v>
       </c>
       <c r="N32">
-        <v>46.993928</v>
+        <v>46.5137256</v>
       </c>
       <c r="O32">
-        <v>10.33866416</v>
+        <v>10.233019632</v>
       </c>
       <c r="P32">
-        <v>36.65526384</v>
+        <v>36.280705968</v>
       </c>
       <c r="Q32">
-        <v>46.15526384</v>
+        <v>45.78070596800001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1150684770724821</v>
+        <v>0.1159068442654271</v>
       </c>
       <c r="T32">
-        <v>0.9028004650714011</v>
+        <v>0.9137272000550416</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.262091706885818</v>
+        <v>4.124604877631437</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4058,22 +4058,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09395176254314469</v>
+        <v>0.09470399113555196</v>
       </c>
       <c r="C33">
-        <v>641.4013952371462</v>
+        <v>619.7243631604254</v>
       </c>
       <c r="D33">
-        <v>869.1493952371462</v>
+        <v>855.7803631604254</v>
       </c>
       <c r="E33">
-        <v>147.448</v>
+        <v>155.7560000000001</v>
       </c>
       <c r="F33">
-        <v>257.548</v>
+        <v>265.8560000000001</v>
       </c>
       <c r="G33">
         <v>29.8</v>
@@ -4094,45 +4094,45 @@
         <v>61.4</v>
       </c>
       <c r="M33">
-        <v>14.8862744</v>
+        <v>16.2969728</v>
       </c>
       <c r="N33">
-        <v>46.5137256</v>
+        <v>45.1030272</v>
       </c>
       <c r="O33">
-        <v>10.233019632</v>
+        <v>9.922665984</v>
       </c>
       <c r="P33">
-        <v>36.280705968</v>
+        <v>35.180361216</v>
       </c>
       <c r="Q33">
-        <v>45.78070596800001</v>
+        <v>44.68036121600001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1159068442654271</v>
+        <v>0.1167698693169882</v>
       </c>
       <c r="T33">
-        <v>0.9137272000550416</v>
+        <v>0.9249753095970245</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.124604877631437</v>
+        <v>3.767570870585241</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4140,22 +4140,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09470399113555196</v>
+        <v>0.09460991972795921</v>
       </c>
       <c r="C34">
-        <v>619.7243631604254</v>
+        <v>613.0657095187357</v>
       </c>
       <c r="D34">
-        <v>855.7803631604254</v>
+        <v>857.4297095187359</v>
       </c>
       <c r="E34">
-        <v>155.7560000000001</v>
+        <v>164.064</v>
       </c>
       <c r="F34">
-        <v>265.8560000000001</v>
+        <v>274.164</v>
       </c>
       <c r="G34">
         <v>29.8</v>
@@ -4176,28 +4176,28 @@
         <v>61.4</v>
       </c>
       <c r="M34">
-        <v>16.2969728</v>
+        <v>16.8062532</v>
       </c>
       <c r="N34">
-        <v>45.1030272</v>
+        <v>44.59374679999999</v>
       </c>
       <c r="O34">
-        <v>9.922665984</v>
+        <v>9.810624295999999</v>
       </c>
       <c r="P34">
-        <v>35.180361216</v>
+        <v>34.78312250399999</v>
       </c>
       <c r="Q34">
-        <v>44.68036121600001</v>
+        <v>44.283122504</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1167698693169882</v>
+        <v>0.1176586563103869</v>
       </c>
       <c r="T34">
-        <v>0.9249753095970245</v>
+        <v>0.936559183602947</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.767570870585241</v>
+        <v>3.653402056325081</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4222,22 +4222,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09460991972795921</v>
+        <v>0.09451584832036647</v>
       </c>
       <c r="C35">
-        <v>613.0657095187357</v>
+        <v>606.41342572747</v>
       </c>
       <c r="D35">
-        <v>857.4297095187359</v>
+        <v>859.08542572747</v>
       </c>
       <c r="E35">
-        <v>164.064</v>
+        <v>172.372</v>
       </c>
       <c r="F35">
-        <v>274.164</v>
+        <v>282.472</v>
       </c>
       <c r="G35">
         <v>29.8</v>
@@ -4258,28 +4258,28 @@
         <v>61.4</v>
       </c>
       <c r="M35">
-        <v>16.8062532</v>
+        <v>17.3155336</v>
       </c>
       <c r="N35">
-        <v>44.59374679999999</v>
+        <v>44.0844664</v>
       </c>
       <c r="O35">
-        <v>9.810624295999999</v>
+        <v>9.698582607999999</v>
       </c>
       <c r="P35">
-        <v>34.78312250399999</v>
+        <v>34.385883792</v>
       </c>
       <c r="Q35">
-        <v>44.283122504</v>
+        <v>43.88588379200001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1176586563103869</v>
+        <v>0.1185743762429795</v>
       </c>
       <c r="T35">
-        <v>0.936559183602947</v>
+        <v>0.9484940840938976</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.653402056325081</v>
+        <v>3.545949054668462</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4304,22 +4304,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09451584832036647</v>
+        <v>0.09518617691277374</v>
       </c>
       <c r="C36">
-        <v>606.41342572747</v>
+        <v>586.4448850623644</v>
       </c>
       <c r="D36">
-        <v>859.08542572747</v>
+        <v>847.4248850623644</v>
       </c>
       <c r="E36">
-        <v>172.372</v>
+        <v>180.68</v>
       </c>
       <c r="F36">
-        <v>282.472</v>
+        <v>290.78</v>
       </c>
       <c r="G36">
         <v>29.8</v>
@@ -4340,45 +4340,45 @@
         <v>61.4</v>
       </c>
       <c r="M36">
-        <v>17.3155336</v>
+        <v>18.638998</v>
       </c>
       <c r="N36">
-        <v>44.0844664</v>
+        <v>42.76100199999999</v>
       </c>
       <c r="O36">
-        <v>9.698582607999999</v>
+        <v>9.407420439999997</v>
       </c>
       <c r="P36">
-        <v>34.385883792</v>
+        <v>33.35358155999999</v>
       </c>
       <c r="Q36">
-        <v>43.88588379200001</v>
+        <v>42.85358156</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1185743762429795</v>
+        <v>0.1195182721734981</v>
       </c>
       <c r="T36">
-        <v>0.9484940840938976</v>
+        <v>0.9607962122922621</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.22</v>
       </c>
       <c r="W36">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.545949054668462</v>
+        <v>3.294168495538225</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4386,22 +4386,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09518617691277374</v>
+        <v>0.095113945505181</v>
       </c>
       <c r="C37">
-        <v>586.4448850623644</v>
+        <v>579.3781301432458</v>
       </c>
       <c r="D37">
-        <v>847.4248850623644</v>
+        <v>848.6661301432459</v>
       </c>
       <c r="E37">
-        <v>180.68</v>
+        <v>188.9880000000001</v>
       </c>
       <c r="F37">
-        <v>290.78</v>
+        <v>299.0880000000001</v>
       </c>
       <c r="G37">
         <v>29.8</v>
@@ -4422,28 +4422,28 @@
         <v>61.4</v>
       </c>
       <c r="M37">
-        <v>18.638998</v>
+        <v>19.17154080000001</v>
       </c>
       <c r="N37">
-        <v>42.76100199999999</v>
+        <v>42.22845919999999</v>
       </c>
       <c r="O37">
-        <v>9.407420439999997</v>
+        <v>9.290261023999998</v>
       </c>
       <c r="P37">
-        <v>33.35358155999999</v>
+        <v>32.93819817599999</v>
       </c>
       <c r="Q37">
-        <v>42.85358156</v>
+        <v>42.438198176</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1195182721734981</v>
+        <v>0.1204916648518453</v>
       </c>
       <c r="T37">
-        <v>0.9607962122922621</v>
+        <v>0.9734827819968255</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.294168495538225</v>
+        <v>3.202663815106607</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4468,22 +4468,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09511394550518099</v>
+        <v>0.09504171409758824</v>
       </c>
       <c r="C38">
-        <v>579.3781301432462</v>
+        <v>572.315016725282</v>
       </c>
       <c r="D38">
-        <v>848.6661301432462</v>
+        <v>849.9110167252821</v>
       </c>
       <c r="E38">
-        <v>188.988</v>
+        <v>197.296</v>
       </c>
       <c r="F38">
-        <v>299.088</v>
+        <v>307.396</v>
       </c>
       <c r="G38">
         <v>29.8</v>
@@ -4504,28 +4504,28 @@
         <v>61.4</v>
       </c>
       <c r="M38">
-        <v>19.1715408</v>
+        <v>19.7040836</v>
       </c>
       <c r="N38">
-        <v>42.2284592</v>
+        <v>41.6959164</v>
       </c>
       <c r="O38">
-        <v>9.290261023999999</v>
+        <v>9.173101608</v>
       </c>
       <c r="P38">
-        <v>32.938198176</v>
+        <v>32.52281479200001</v>
       </c>
       <c r="Q38">
-        <v>42.43819817600001</v>
+        <v>42.02281479200001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1204916648518453</v>
+        <v>0.1214959588850607</v>
       </c>
       <c r="T38">
-        <v>0.9734827819968253</v>
+        <v>0.9865720999459779</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.202663815106608</v>
+        <v>3.116105333617241</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4550,22 +4550,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09504171409758824</v>
+        <v>0.0949694826899955</v>
       </c>
       <c r="C39">
-        <v>572.315016725282</v>
+        <v>565.2555608568871</v>
       </c>
       <c r="D39">
-        <v>849.9110167252821</v>
+        <v>851.1595608568871</v>
       </c>
       <c r="E39">
-        <v>197.296</v>
+        <v>205.604</v>
       </c>
       <c r="F39">
-        <v>307.396</v>
+        <v>315.704</v>
       </c>
       <c r="G39">
         <v>29.8</v>
@@ -4586,28 +4586,28 @@
         <v>61.4</v>
       </c>
       <c r="M39">
-        <v>19.7040836</v>
+        <v>20.2366264</v>
       </c>
       <c r="N39">
-        <v>41.6959164</v>
+        <v>41.1633736</v>
       </c>
       <c r="O39">
-        <v>9.173101608</v>
+        <v>9.055942192</v>
       </c>
       <c r="P39">
-        <v>32.52281479200001</v>
+        <v>32.107431408</v>
       </c>
       <c r="Q39">
-        <v>42.02281479200001</v>
+        <v>41.607431408</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1214959588850607</v>
+        <v>0.1225326494999927</v>
       </c>
       <c r="T39">
-        <v>0.9865720999459779</v>
+        <v>1.000083653958006</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.116105333617241</v>
+        <v>3.034102561679945</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4632,22 +4632,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0949694826899955</v>
+        <v>0.09727001128240276</v>
       </c>
       <c r="C40">
-        <v>565.2555608568871</v>
+        <v>518.9037202268861</v>
       </c>
       <c r="D40">
-        <v>851.1595608568871</v>
+        <v>813.1157202268862</v>
       </c>
       <c r="E40">
-        <v>205.604</v>
+        <v>213.9120000000001</v>
       </c>
       <c r="F40">
-        <v>315.704</v>
+        <v>324.0120000000001</v>
       </c>
       <c r="G40">
         <v>29.8</v>
@@ -4668,45 +4668,45 @@
         <v>61.4</v>
       </c>
       <c r="M40">
-        <v>20.2366264</v>
+        <v>23.29646280000001</v>
       </c>
       <c r="N40">
-        <v>41.1633736</v>
+        <v>38.10353719999999</v>
       </c>
       <c r="O40">
-        <v>9.055942192</v>
+        <v>8.382778183999998</v>
       </c>
       <c r="P40">
-        <v>32.107431408</v>
+        <v>29.720759016</v>
       </c>
       <c r="Q40">
-        <v>41.607431408</v>
+        <v>39.220759016</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1225326494999927</v>
+        <v>0.1236033299711521</v>
       </c>
       <c r="T40">
-        <v>1.000083653958006</v>
+        <v>1.014038209740921</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0.22</v>
       </c>
       <c r="W40">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.034102561679945</v>
+        <v>2.635593245511932</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4714,22 +4714,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09727001128240276</v>
+        <v>0.09725861987481001</v>
       </c>
       <c r="C41">
-        <v>518.9037202268861</v>
+        <v>510.775719857885</v>
       </c>
       <c r="D41">
-        <v>813.1157202268862</v>
+        <v>813.295719857885</v>
       </c>
       <c r="E41">
-        <v>213.9120000000001</v>
+        <v>222.2200000000001</v>
       </c>
       <c r="F41">
-        <v>324.0120000000001</v>
+        <v>332.3200000000001</v>
       </c>
       <c r="G41">
         <v>29.8</v>
@@ -4750,28 +4750,28 @@
         <v>61.4</v>
       </c>
       <c r="M41">
-        <v>23.29646280000001</v>
+        <v>23.89380800000001</v>
       </c>
       <c r="N41">
-        <v>38.10353719999999</v>
+        <v>37.50619199999999</v>
       </c>
       <c r="O41">
-        <v>8.382778183999998</v>
+        <v>8.251362239999999</v>
       </c>
       <c r="P41">
-        <v>29.720759016</v>
+        <v>29.25482975999999</v>
       </c>
       <c r="Q41">
-        <v>39.220759016</v>
+        <v>38.75482976</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1236033299711521</v>
+        <v>0.12470969979135</v>
       </c>
       <c r="T41">
-        <v>1.014038209740921</v>
+        <v>1.028457917383266</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.635593245511932</v>
+        <v>2.569703414374133</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4796,22 +4796,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09725861987481001</v>
+        <v>0.09724722846721726</v>
       </c>
       <c r="C42">
-        <v>510.775719857885</v>
+        <v>502.6477991996566</v>
       </c>
       <c r="D42">
-        <v>813.295719857885</v>
+        <v>813.4757991996566</v>
       </c>
       <c r="E42">
-        <v>222.2200000000001</v>
+        <v>230.528</v>
       </c>
       <c r="F42">
-        <v>332.3200000000001</v>
+        <v>340.628</v>
       </c>
       <c r="G42">
         <v>29.8</v>
@@ -4832,28 +4832,28 @@
         <v>61.4</v>
       </c>
       <c r="M42">
-        <v>23.89380800000001</v>
+        <v>24.49115320000001</v>
       </c>
       <c r="N42">
-        <v>37.50619199999999</v>
+        <v>36.90884679999999</v>
       </c>
       <c r="O42">
-        <v>8.251362239999999</v>
+        <v>8.119946295999998</v>
       </c>
       <c r="P42">
-        <v>29.25482975999999</v>
+        <v>28.78890050399999</v>
       </c>
       <c r="Q42">
-        <v>38.75482976</v>
+        <v>38.288900504</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.12470969979135</v>
+        <v>0.1258535736732496</v>
       </c>
       <c r="T42">
-        <v>1.028457917383266</v>
+        <v>1.043366428674505</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.569703414374133</v>
+        <v>2.507027721340618</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4878,22 +4878,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09724722846721726</v>
+        <v>0.09851347705962453</v>
       </c>
       <c r="C43">
-        <v>502.6477991996566</v>
+        <v>474.7990167821196</v>
       </c>
       <c r="D43">
-        <v>813.4757991996566</v>
+        <v>793.9350167821196</v>
       </c>
       <c r="E43">
-        <v>230.528</v>
+        <v>238.836</v>
       </c>
       <c r="F43">
-        <v>340.628</v>
+        <v>348.936</v>
       </c>
       <c r="G43">
         <v>29.8</v>
@@ -4914,45 +4914,45 @@
         <v>61.4</v>
       </c>
       <c r="M43">
-        <v>24.49115320000001</v>
+        <v>26.44934880000001</v>
       </c>
       <c r="N43">
-        <v>36.90884679999999</v>
+        <v>34.9506512</v>
       </c>
       <c r="O43">
-        <v>8.119946295999998</v>
+        <v>7.689143263999999</v>
       </c>
       <c r="P43">
-        <v>28.78890050399999</v>
+        <v>27.261507936</v>
       </c>
       <c r="Q43">
-        <v>38.288900504</v>
+        <v>36.761507936</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1258535736732496</v>
+        <v>0.1270368914821113</v>
       </c>
       <c r="T43">
-        <v>1.043366428674505</v>
+        <v>1.058789026561992</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.22</v>
       </c>
       <c r="W43">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.507027721340618</v>
+        <v>2.32141821200528</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4960,22 +4960,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09851347705962454</v>
+        <v>0.0985325056520318</v>
       </c>
       <c r="C44">
-        <v>474.7990167821193</v>
+        <v>466.2045243113863</v>
       </c>
       <c r="D44">
-        <v>793.9350167821194</v>
+        <v>793.6485243113864</v>
       </c>
       <c r="E44">
-        <v>238.836</v>
+        <v>247.144</v>
       </c>
       <c r="F44">
-        <v>348.936</v>
+        <v>357.244</v>
       </c>
       <c r="G44">
         <v>29.8</v>
@@ -4996,28 +4996,28 @@
         <v>61.4</v>
       </c>
       <c r="M44">
-        <v>26.44934880000001</v>
+        <v>27.0790952</v>
       </c>
       <c r="N44">
-        <v>34.9506512</v>
+        <v>34.32090479999999</v>
       </c>
       <c r="O44">
-        <v>7.689143263999999</v>
+        <v>7.550599055999998</v>
       </c>
       <c r="P44">
-        <v>27.261507936</v>
+        <v>26.77030574399999</v>
       </c>
       <c r="Q44">
-        <v>36.761507936</v>
+        <v>36.270305744</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1270368914821113</v>
+        <v>0.1282617292140908</v>
       </c>
       <c r="T44">
-        <v>1.058789026561992</v>
+        <v>1.074752768235006</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -5034,7 +5034,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.32141821200528</v>
+        <v>2.267431741958645</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5042,22 +5042,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0985325056520318</v>
+        <v>0.09855153424443906</v>
       </c>
       <c r="C45">
-        <v>466.2045243113863</v>
+        <v>457.6102385284217</v>
       </c>
       <c r="D45">
-        <v>793.6485243113864</v>
+        <v>793.3622385284218</v>
       </c>
       <c r="E45">
-        <v>247.144</v>
+        <v>255.452</v>
       </c>
       <c r="F45">
-        <v>357.244</v>
+        <v>365.552</v>
       </c>
       <c r="G45">
         <v>29.8</v>
@@ -5078,28 +5078,28 @@
         <v>61.4</v>
       </c>
       <c r="M45">
-        <v>27.0790952</v>
+        <v>27.7088416</v>
       </c>
       <c r="N45">
-        <v>34.32090479999999</v>
+        <v>33.69115839999999</v>
       </c>
       <c r="O45">
-        <v>7.550599055999998</v>
+        <v>7.412054847999999</v>
       </c>
       <c r="P45">
-        <v>26.77030574399999</v>
+        <v>26.279103552</v>
       </c>
       <c r="Q45">
-        <v>36.270305744</v>
+        <v>35.779103552</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1282617292140908</v>
+        <v>0.129530311150784</v>
       </c>
       <c r="T45">
-        <v>1.074752768235006</v>
+        <v>1.091286643539199</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.267431741958645</v>
+        <v>2.215899202368676</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5124,22 +5124,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09855153424443906</v>
+        <v>0.09857056283684631</v>
       </c>
       <c r="C46">
-        <v>457.6102385284217</v>
+        <v>449.016159209637</v>
       </c>
       <c r="D46">
-        <v>793.3622385284218</v>
+        <v>793.076159209637</v>
       </c>
       <c r="E46">
-        <v>255.452</v>
+        <v>263.76</v>
       </c>
       <c r="F46">
-        <v>365.552</v>
+        <v>373.86</v>
       </c>
       <c r="G46">
         <v>29.8</v>
@@ -5160,28 +5160,28 @@
         <v>61.4</v>
       </c>
       <c r="M46">
-        <v>27.7088416</v>
+        <v>28.338588</v>
       </c>
       <c r="N46">
-        <v>33.69115839999999</v>
+        <v>33.06141199999999</v>
       </c>
       <c r="O46">
-        <v>7.412054847999999</v>
+        <v>7.273510639999998</v>
       </c>
       <c r="P46">
-        <v>26.279103552</v>
+        <v>25.78790135999999</v>
       </c>
       <c r="Q46">
-        <v>35.779103552</v>
+        <v>35.28790136</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.129530311150784</v>
+        <v>0.1308450233397205</v>
       </c>
       <c r="T46">
-        <v>1.091286643539199</v>
+        <v>1.108421750672635</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.215899202368676</v>
+        <v>2.166656997871594</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5206,22 +5206,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09857056283684631</v>
+        <v>0.09858959142925357</v>
       </c>
       <c r="C47">
-        <v>449.016159209637</v>
+        <v>440.4222861317645</v>
       </c>
       <c r="D47">
-        <v>793.076159209637</v>
+        <v>792.7902861317646</v>
       </c>
       <c r="E47">
-        <v>263.76</v>
+        <v>272.0680000000001</v>
       </c>
       <c r="F47">
-        <v>373.86</v>
+        <v>382.1680000000001</v>
       </c>
       <c r="G47">
         <v>29.8</v>
@@ -5242,28 +5242,28 @@
         <v>61.4</v>
       </c>
       <c r="M47">
-        <v>28.338588</v>
+        <v>28.96833440000001</v>
       </c>
       <c r="N47">
-        <v>33.06141199999999</v>
+        <v>32.43166559999999</v>
       </c>
       <c r="O47">
-        <v>7.273510639999998</v>
+        <v>7.134966431999997</v>
       </c>
       <c r="P47">
-        <v>25.78790135999999</v>
+        <v>25.29669916799999</v>
       </c>
       <c r="Q47">
-        <v>35.28790136</v>
+        <v>34.796699168</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1308450233397205</v>
+        <v>0.1322084285726918</v>
       </c>
       <c r="T47">
-        <v>1.108421750672635</v>
+        <v>1.126191491403606</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.166656997871594</v>
+        <v>2.119555758787429</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5288,22 +5288,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09858959142925357</v>
+        <v>0.09860862002166082</v>
       </c>
       <c r="C48">
-        <v>440.4222861317645</v>
+        <v>431.8286190718594</v>
       </c>
       <c r="D48">
-        <v>792.7902861317646</v>
+        <v>792.5046190718595</v>
       </c>
       <c r="E48">
-        <v>272.0680000000001</v>
+        <v>280.3760000000001</v>
       </c>
       <c r="F48">
-        <v>382.1680000000001</v>
+        <v>390.4760000000001</v>
       </c>
       <c r="G48">
         <v>29.8</v>
@@ -5324,28 +5324,28 @@
         <v>61.4</v>
       </c>
       <c r="M48">
-        <v>28.96833440000001</v>
+        <v>29.59808080000001</v>
       </c>
       <c r="N48">
-        <v>32.43166559999999</v>
+        <v>31.80191919999999</v>
       </c>
       <c r="O48">
-        <v>7.134966431999997</v>
+        <v>6.996422223999999</v>
       </c>
       <c r="P48">
-        <v>25.29669916799999</v>
+        <v>24.80549697599999</v>
       </c>
       <c r="Q48">
-        <v>34.796699168</v>
+        <v>34.305496976</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1322084285726918</v>
+        <v>0.1336232830597374</v>
       </c>
       <c r="T48">
-        <v>1.126191491403606</v>
+        <v>1.144631788388576</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.119555758787429</v>
+        <v>2.074458827749399</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5370,22 +5370,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09860862002166082</v>
+        <v>0.09862764861406807</v>
       </c>
       <c r="C49">
-        <v>431.8286190718594</v>
+        <v>423.2351578072979</v>
       </c>
       <c r="D49">
-        <v>792.5046190718595</v>
+        <v>792.219157807298</v>
       </c>
       <c r="E49">
-        <v>280.3760000000001</v>
+        <v>288.6840000000001</v>
       </c>
       <c r="F49">
-        <v>390.4760000000001</v>
+        <v>398.784</v>
       </c>
       <c r="G49">
         <v>29.8</v>
@@ -5406,28 +5406,28 @@
         <v>61.4</v>
       </c>
       <c r="M49">
-        <v>29.59808080000001</v>
+        <v>30.22782720000001</v>
       </c>
       <c r="N49">
-        <v>31.80191919999999</v>
+        <v>31.17217279999999</v>
       </c>
       <c r="O49">
-        <v>6.996422223999999</v>
+        <v>6.857878015999998</v>
       </c>
       <c r="P49">
-        <v>24.80549697599999</v>
+        <v>24.31429478399999</v>
       </c>
       <c r="Q49">
-        <v>34.305496976</v>
+        <v>33.814294784</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1336232830597374</v>
+        <v>0.135092555027054</v>
       </c>
       <c r="T49">
-        <v>1.144631788388576</v>
+        <v>1.163781327565275</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.074458827749399</v>
+        <v>2.031240935504619</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5452,22 +5452,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09862764861406807</v>
+        <v>0.1040739172064753</v>
       </c>
       <c r="C50">
-        <v>423.2351578072979</v>
+        <v>340.886514509171</v>
       </c>
       <c r="D50">
-        <v>792.219157807298</v>
+        <v>718.1785145091711</v>
       </c>
       <c r="E50">
-        <v>288.684</v>
+        <v>296.9920000000001</v>
       </c>
       <c r="F50">
-        <v>398.784</v>
+        <v>407.092</v>
       </c>
       <c r="G50">
         <v>29.8</v>
@@ -5488,45 +5488,45 @@
         <v>61.4</v>
       </c>
       <c r="M50">
-        <v>30.2278272</v>
+        <v>36.63828</v>
       </c>
       <c r="N50">
-        <v>31.1721728</v>
+        <v>24.76172</v>
       </c>
       <c r="O50">
-        <v>6.857878016</v>
+        <v>5.447578399999999</v>
       </c>
       <c r="P50">
-        <v>24.314294784</v>
+        <v>19.3141416</v>
       </c>
       <c r="Q50">
-        <v>33.814294784</v>
+        <v>28.81414160000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.135092555027054</v>
+        <v>0.1366194455028928</v>
       </c>
       <c r="T50">
-        <v>1.163781327565275</v>
+        <v>1.183681829062629</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V50">
         <v>0.22</v>
       </c>
       <c r="W50">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.03124093550462</v>
+        <v>1.67584286161905</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5534,22 +5534,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1040739172064753</v>
+        <v>0.1042037057988826</v>
       </c>
       <c r="C51">
-        <v>340.886514509171</v>
+        <v>330.982530534862</v>
       </c>
       <c r="D51">
-        <v>718.1785145091711</v>
+        <v>716.582530534862</v>
       </c>
       <c r="E51">
-        <v>296.9920000000001</v>
+        <v>305.3000000000001</v>
       </c>
       <c r="F51">
-        <v>407.092</v>
+        <v>415.4</v>
       </c>
       <c r="G51">
         <v>29.8</v>
@@ -5570,28 +5570,28 @@
         <v>61.4</v>
       </c>
       <c r="M51">
-        <v>36.63828</v>
+        <v>37.386</v>
       </c>
       <c r="N51">
-        <v>24.76172</v>
+        <v>24.014</v>
       </c>
       <c r="O51">
-        <v>5.447578399999999</v>
+        <v>5.283079999999999</v>
       </c>
       <c r="P51">
-        <v>19.3141416</v>
+        <v>18.73092</v>
       </c>
       <c r="Q51">
-        <v>28.81414160000001</v>
+        <v>28.23092</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1366194455028928</v>
+        <v>0.1382074115977651</v>
       </c>
       <c r="T51">
-        <v>1.183681829062629</v>
+        <v>1.204378350619878</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.67584286161905</v>
+        <v>1.642326004386669</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5616,22 +5616,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1042037057988826</v>
+        <v>0.1043334943912898</v>
       </c>
       <c r="C52">
-        <v>330.982530534862</v>
+        <v>321.0856242351625</v>
       </c>
       <c r="D52">
-        <v>716.582530534862</v>
+        <v>714.9936242351625</v>
       </c>
       <c r="E52">
-        <v>305.3000000000001</v>
+        <v>313.6080000000001</v>
       </c>
       <c r="F52">
-        <v>415.4</v>
+        <v>423.708</v>
       </c>
       <c r="G52">
         <v>29.8</v>
@@ -5652,28 +5652,28 @@
         <v>61.4</v>
       </c>
       <c r="M52">
-        <v>37.386</v>
+        <v>38.13372</v>
       </c>
       <c r="N52">
-        <v>24.014</v>
+        <v>23.26627999999999</v>
       </c>
       <c r="O52">
-        <v>5.283079999999999</v>
+        <v>5.118581599999999</v>
       </c>
       <c r="P52">
-        <v>18.73092</v>
+        <v>18.1476984</v>
       </c>
       <c r="Q52">
-        <v>28.23092</v>
+        <v>27.6476984</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1382074115977651</v>
+        <v>0.1398601926352854</v>
       </c>
       <c r="T52">
-        <v>1.204378350619878</v>
+        <v>1.225919628159055</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.642326004386669</v>
+        <v>1.61012353371242</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5698,22 +5698,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1043334943912898</v>
+        <v>0.1044632829836971</v>
       </c>
       <c r="C53">
-        <v>321.0856242351625</v>
+        <v>311.1957486334264</v>
       </c>
       <c r="D53">
-        <v>714.9936242351625</v>
+        <v>713.4117486334266</v>
       </c>
       <c r="E53">
-        <v>313.6080000000001</v>
+        <v>321.9160000000001</v>
       </c>
       <c r="F53">
-        <v>423.708</v>
+        <v>432.0160000000001</v>
       </c>
       <c r="G53">
         <v>29.8</v>
@@ -5734,28 +5734,28 @@
         <v>61.4</v>
       </c>
       <c r="M53">
-        <v>38.13372</v>
+        <v>38.88144</v>
       </c>
       <c r="N53">
-        <v>23.26627999999999</v>
+        <v>22.51855999999999</v>
       </c>
       <c r="O53">
-        <v>5.118581599999999</v>
+        <v>4.954083199999999</v>
       </c>
       <c r="P53">
-        <v>18.1476984</v>
+        <v>17.56447679999999</v>
       </c>
       <c r="Q53">
-        <v>27.6476984</v>
+        <v>27.0644768</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1398601926352854</v>
+        <v>0.141581839549369</v>
       </c>
       <c r="T53">
-        <v>1.225919628159055</v>
+        <v>1.248358458929031</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.61012353371242</v>
+        <v>1.579159619602566</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5780,22 +5780,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1044632829836971</v>
+        <v>0.1045930715761043</v>
       </c>
       <c r="C54">
-        <v>311.1957486334264</v>
+        <v>301.3128571678211</v>
       </c>
       <c r="D54">
-        <v>713.4117486334266</v>
+        <v>711.8368571678212</v>
       </c>
       <c r="E54">
-        <v>321.9160000000001</v>
+        <v>330.224</v>
       </c>
       <c r="F54">
-        <v>432.0160000000001</v>
+        <v>440.3240000000001</v>
       </c>
       <c r="G54">
         <v>29.8</v>
@@ -5816,28 +5816,28 @@
         <v>61.4</v>
       </c>
       <c r="M54">
-        <v>38.88144</v>
+        <v>39.62916000000001</v>
       </c>
       <c r="N54">
-        <v>22.51855999999999</v>
+        <v>21.77083999999999</v>
       </c>
       <c r="O54">
-        <v>4.954083199999999</v>
+        <v>4.789584799999998</v>
       </c>
       <c r="P54">
-        <v>17.56447679999999</v>
+        <v>16.98125519999999</v>
       </c>
       <c r="Q54">
-        <v>27.0644768</v>
+        <v>26.4812552</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.141581839549369</v>
+        <v>0.1433767480342646</v>
       </c>
       <c r="T54">
-        <v>1.248358458929031</v>
+        <v>1.271752133561559</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.579159619602566</v>
+        <v>1.549364155081763</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5862,22 +5862,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1045930715761043</v>
+        <v>0.1047228601685116</v>
       </c>
       <c r="C55">
-        <v>301.3128571678211</v>
+        <v>291.436903686758</v>
       </c>
       <c r="D55">
-        <v>711.8368571678212</v>
+        <v>710.2689036867581</v>
       </c>
       <c r="E55">
-        <v>330.224</v>
+        <v>338.532</v>
       </c>
       <c r="F55">
-        <v>440.3240000000001</v>
+        <v>448.6320000000001</v>
       </c>
       <c r="G55">
         <v>29.8</v>
@@ -5898,28 +5898,28 @@
         <v>61.4</v>
       </c>
       <c r="M55">
-        <v>39.62916000000001</v>
+        <v>40.37688000000001</v>
       </c>
       <c r="N55">
-        <v>21.77083999999999</v>
+        <v>21.02311999999999</v>
       </c>
       <c r="O55">
-        <v>4.789584799999998</v>
+        <v>4.625086399999998</v>
       </c>
       <c r="P55">
-        <v>16.98125519999999</v>
+        <v>16.39803359999999</v>
       </c>
       <c r="Q55">
-        <v>26.4812552</v>
+        <v>25.8980336</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1433767480342646</v>
+        <v>0.1452496960185035</v>
       </c>
       <c r="T55">
-        <v>1.271752133561559</v>
+        <v>1.296162924482458</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5936,7 +5936,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.549364155081763</v>
+        <v>1.520672226283952</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5944,22 +5944,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1047228601685116</v>
+        <v>0.1312554146677058</v>
       </c>
       <c r="C56">
-        <v>291.436903686758</v>
+        <v>62.601644303233</v>
       </c>
       <c r="D56">
-        <v>710.2689036867581</v>
+        <v>489.7416443032331</v>
       </c>
       <c r="E56">
-        <v>338.532</v>
+        <v>346.84</v>
       </c>
       <c r="F56">
-        <v>448.6320000000001</v>
+        <v>456.9400000000001</v>
       </c>
       <c r="G56">
         <v>29.8</v>
@@ -5980,45 +5980,45 @@
         <v>61.4</v>
       </c>
       <c r="M56">
-        <v>40.37688000000001</v>
+        <v>67.07879200000002</v>
       </c>
       <c r="N56">
-        <v>21.02311999999999</v>
+        <v>-5.678792000000023</v>
       </c>
       <c r="O56">
-        <v>4.625086399999998</v>
+        <v>-1.249334240000005</v>
       </c>
       <c r="P56">
-        <v>16.39803359999999</v>
+        <v>-4.429457760000018</v>
       </c>
       <c r="Q56">
-        <v>25.8980336</v>
+        <v>5.070542239999989</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1452496960185035</v>
+        <v>0.148387649135853</v>
       </c>
       <c r="T56">
-        <v>1.296162924482458</v>
+        <v>1.337060972966344</v>
       </c>
       <c r="U56">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.22</v>
+        <v>0.2013751231536787</v>
       </c>
       <c r="W56">
-        <v>0.0702</v>
+        <v>0.11723813192104</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.520672226283952</v>
+        <v>0.9153414688803576</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6026,22 +6026,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1312554146677058</v>
+        <v>0.1322654146677058</v>
       </c>
       <c r="C57">
-        <v>62.601644303233</v>
+        <v>48.57298636563797</v>
       </c>
       <c r="D57">
-        <v>489.7416443032331</v>
+        <v>484.0209863656381</v>
       </c>
       <c r="E57">
-        <v>346.84</v>
+        <v>355.1480000000001</v>
       </c>
       <c r="F57">
-        <v>456.9400000000001</v>
+        <v>465.2480000000001</v>
       </c>
       <c r="G57">
         <v>29.8</v>
@@ -6062,37 +6062,37 @@
         <v>61.4</v>
       </c>
       <c r="M57">
-        <v>67.07879200000002</v>
+        <v>68.29840640000002</v>
       </c>
       <c r="N57">
-        <v>-5.678792000000023</v>
+        <v>-6.89840640000002</v>
       </c>
       <c r="O57">
-        <v>-1.249334240000005</v>
+        <v>-1.517649408000004</v>
       </c>
       <c r="P57">
-        <v>-4.429457760000018</v>
+        <v>-5.380756992000016</v>
       </c>
       <c r="Q57">
-        <v>5.070542239999989</v>
+        <v>4.119243007999991</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.148387649135853</v>
+        <v>0.1507191866162133</v>
       </c>
       <c r="T57">
-        <v>1.337060972966344</v>
+        <v>1.367448722351943</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2013751231536787</v>
+        <v>0.1977791388116487</v>
       </c>
       <c r="W57">
-        <v>0.11723813192104</v>
+        <v>0.11776602242245</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9153414688803576</v>
+        <v>0.8989960855074941</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6108,22 +6108,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1322654146677058</v>
+        <v>0.1332754146677058</v>
       </c>
       <c r="C58">
-        <v>48.57298636563797</v>
+        <v>34.67643102027222</v>
       </c>
       <c r="D58">
-        <v>484.0209863656381</v>
+        <v>478.4324310202723</v>
       </c>
       <c r="E58">
-        <v>355.1480000000001</v>
+        <v>363.4560000000001</v>
       </c>
       <c r="F58">
-        <v>465.2480000000001</v>
+        <v>473.5560000000001</v>
       </c>
       <c r="G58">
         <v>29.8</v>
@@ -6144,37 +6144,37 @@
         <v>61.4</v>
       </c>
       <c r="M58">
-        <v>68.29840640000002</v>
+        <v>69.51802080000002</v>
       </c>
       <c r="N58">
-        <v>-6.89840640000002</v>
+        <v>-8.118020800000018</v>
       </c>
       <c r="O58">
-        <v>-1.517649408000004</v>
+        <v>-1.785964576000004</v>
       </c>
       <c r="P58">
-        <v>-5.380756992000016</v>
+        <v>-6.332056224000014</v>
       </c>
       <c r="Q58">
-        <v>4.119243007999991</v>
+        <v>3.167943775999993</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1507191866162133</v>
+        <v>0.1531591677003112</v>
       </c>
       <c r="T58">
-        <v>1.367448722351943</v>
+        <v>1.399249855429895</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1977791388116487</v>
+        <v>0.1943093293588128</v>
       </c>
       <c r="W58">
-        <v>0.11776602242245</v>
+        <v>0.1182753904501263</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8989960855074941</v>
+        <v>0.8832242243582399</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6190,22 +6190,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1332754146677058</v>
+        <v>0.1342854146677058</v>
       </c>
       <c r="C59">
-        <v>34.67643102027222</v>
+        <v>20.9074546871089</v>
       </c>
       <c r="D59">
-        <v>478.4324310202723</v>
+        <v>472.971454687109</v>
       </c>
       <c r="E59">
-        <v>363.4560000000001</v>
+        <v>371.7640000000001</v>
       </c>
       <c r="F59">
-        <v>473.5560000000001</v>
+        <v>481.8640000000001</v>
       </c>
       <c r="G59">
         <v>29.8</v>
@@ -6226,37 +6226,37 @@
         <v>61.4</v>
       </c>
       <c r="M59">
-        <v>69.51802080000002</v>
+        <v>70.73763520000001</v>
       </c>
       <c r="N59">
-        <v>-8.118020800000018</v>
+        <v>-9.337635200000015</v>
       </c>
       <c r="O59">
-        <v>-1.785964576000004</v>
+        <v>-2.054279744000004</v>
       </c>
       <c r="P59">
-        <v>-6.332056224000014</v>
+        <v>-7.283355456000011</v>
       </c>
       <c r="Q59">
-        <v>3.167943775999993</v>
+        <v>2.216644543999996</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1531591677003112</v>
+        <v>0.1557153383598424</v>
       </c>
       <c r="T59">
-        <v>1.399249855429895</v>
+        <v>1.432565328178226</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1943093293588128</v>
+        <v>0.1909591685077988</v>
       </c>
       <c r="W59">
-        <v>0.1182753904501263</v>
+        <v>0.1187671940630552</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8832242243582399</v>
+        <v>0.8679962204899944</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6272,22 +6272,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1342854146677058</v>
+        <v>0.1352954146677058</v>
       </c>
       <c r="C60">
-        <v>20.90745468710895</v>
+        <v>7.261737989469793</v>
       </c>
       <c r="D60">
-        <v>472.971454687109</v>
+        <v>467.6337379894698</v>
       </c>
       <c r="E60">
-        <v>371.764</v>
+        <v>380.072</v>
       </c>
       <c r="F60">
-        <v>481.864</v>
+        <v>490.172</v>
       </c>
       <c r="G60">
         <v>29.8</v>
@@ -6308,37 +6308,37 @@
         <v>61.4</v>
       </c>
       <c r="M60">
-        <v>70.73763520000001</v>
+        <v>71.95724960000001</v>
       </c>
       <c r="N60">
-        <v>-9.337635200000015</v>
+        <v>-10.55724960000001</v>
       </c>
       <c r="O60">
-        <v>-2.054279744000004</v>
+        <v>-2.322594912000003</v>
       </c>
       <c r="P60">
-        <v>-7.283355456000011</v>
+        <v>-8.23465468800001</v>
       </c>
       <c r="Q60">
-        <v>2.216644543999996</v>
+        <v>1.265345311999997</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1557153383598424</v>
+        <v>0.1583962002710581</v>
       </c>
       <c r="T60">
-        <v>1.432565328178226</v>
+        <v>1.46750594593867</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1909591685077988</v>
+        <v>0.1877225724313954</v>
       </c>
       <c r="W60">
-        <v>0.1187671940630552</v>
+        <v>0.1192423263670712</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8679962204899944</v>
+        <v>0.8532844201427063</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6354,22 +6354,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1352954146677058</v>
+        <v>0.1363054146677058</v>
       </c>
       <c r="C61">
-        <v>7.261737989469793</v>
+        <v>-6.264845640067506</v>
       </c>
       <c r="D61">
-        <v>467.6337379894698</v>
+        <v>462.4151543599325</v>
       </c>
       <c r="E61">
-        <v>380.072</v>
+        <v>388.38</v>
       </c>
       <c r="F61">
-        <v>490.172</v>
+        <v>498.48</v>
       </c>
       <c r="G61">
         <v>29.8</v>
@@ -6390,37 +6390,37 @@
         <v>61.4</v>
       </c>
       <c r="M61">
-        <v>71.95724960000001</v>
+        <v>73.17686400000001</v>
       </c>
       <c r="N61">
-        <v>-10.55724960000001</v>
+        <v>-11.77686400000001</v>
       </c>
       <c r="O61">
-        <v>-2.322594912000003</v>
+        <v>-2.590910080000002</v>
       </c>
       <c r="P61">
-        <v>-8.23465468800001</v>
+        <v>-9.185953920000008</v>
       </c>
       <c r="Q61">
-        <v>1.265345311999997</v>
+        <v>0.3140460799999989</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1583962002710581</v>
+        <v>0.1612111052778345</v>
       </c>
       <c r="T61">
-        <v>1.46750594593867</v>
+        <v>1.504193594587137</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1877225724313954</v>
+        <v>0.1845938628908722</v>
       </c>
       <c r="W61">
-        <v>0.1192423263670712</v>
+        <v>0.11970162092762</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8532844201427063</v>
+        <v>0.8390630131403279</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6436,22 +6436,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1363054146677058</v>
+        <v>0.1373154146677058</v>
       </c>
       <c r="C62">
-        <v>-6.264845640067506</v>
+        <v>-19.67624059925953</v>
       </c>
       <c r="D62">
-        <v>462.4151543599325</v>
+        <v>457.3117594007405</v>
       </c>
       <c r="E62">
-        <v>388.38</v>
+        <v>396.688</v>
       </c>
       <c r="F62">
-        <v>498.48</v>
+        <v>506.788</v>
       </c>
       <c r="G62">
         <v>29.8</v>
@@ -6472,37 +6472,37 @@
         <v>61.4</v>
       </c>
       <c r="M62">
-        <v>73.17686400000001</v>
+        <v>74.39647840000001</v>
       </c>
       <c r="N62">
-        <v>-11.77686400000001</v>
+        <v>-12.99647840000001</v>
       </c>
       <c r="O62">
-        <v>-2.590910080000002</v>
+        <v>-2.859225248000002</v>
       </c>
       <c r="P62">
-        <v>-9.185953920000008</v>
+        <v>-10.13725315200001</v>
       </c>
       <c r="Q62">
-        <v>0.3140460799999989</v>
+        <v>-0.6372531519999995</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1612111052778345</v>
+        <v>0.1641703643875226</v>
       </c>
       <c r="T62">
-        <v>1.504193594587137</v>
+        <v>1.542762661115012</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1845938628908722</v>
+        <v>0.1815677339910218</v>
       </c>
       <c r="W62">
-        <v>0.11970162092762</v>
+        <v>0.120145856650118</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8390630131403279</v>
+        <v>0.8253078817773718</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6518,22 +6518,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1373154146677058</v>
+        <v>0.1383254146677058</v>
       </c>
       <c r="C63">
-        <v>-19.67624059925953</v>
+        <v>-32.97621905894601</v>
       </c>
       <c r="D63">
-        <v>457.3117594007405</v>
+        <v>452.319780941054</v>
       </c>
       <c r="E63">
-        <v>396.688</v>
+        <v>404.996</v>
       </c>
       <c r="F63">
-        <v>506.788</v>
+        <v>515.096</v>
       </c>
       <c r="G63">
         <v>29.8</v>
@@ -6554,37 +6554,37 @@
         <v>61.4</v>
       </c>
       <c r="M63">
-        <v>74.39647840000001</v>
+        <v>75.6160928</v>
       </c>
       <c r="N63">
-        <v>-12.99647840000001</v>
+        <v>-14.21609280000001</v>
       </c>
       <c r="O63">
-        <v>-2.859225248000002</v>
+        <v>-3.127540416000001</v>
       </c>
       <c r="P63">
-        <v>-10.13725315200001</v>
+        <v>-11.088552384</v>
       </c>
       <c r="Q63">
-        <v>-0.6372531519999995</v>
+        <v>-1.588552383999996</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1641703643875226</v>
+        <v>0.167285373976668</v>
       </c>
       <c r="T63">
-        <v>1.542762661115012</v>
+        <v>1.583361678512776</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1815677339910218</v>
+        <v>0.1786392221524569</v>
       </c>
       <c r="W63">
-        <v>0.120145856650118</v>
+        <v>0.1205757621880193</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8253078817773718</v>
+        <v>0.8119964643293497</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6600,22 +6600,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1383254146677058</v>
+        <v>0.1749016847854291</v>
       </c>
       <c r="C64">
-        <v>-32.97621905894601</v>
+        <v>-169.4325891966893</v>
       </c>
       <c r="D64">
-        <v>452.319780941054</v>
+        <v>324.1714108033107</v>
       </c>
       <c r="E64">
-        <v>404.996</v>
+        <v>413.304</v>
       </c>
       <c r="F64">
-        <v>515.096</v>
+        <v>523.404</v>
       </c>
       <c r="G64">
         <v>29.8</v>
@@ -6636,45 +6636,45 @@
         <v>61.4</v>
       </c>
       <c r="M64">
-        <v>75.6160928</v>
+        <v>105.0995232</v>
       </c>
       <c r="N64">
-        <v>-14.21609280000001</v>
+        <v>-43.69952320000001</v>
       </c>
       <c r="O64">
-        <v>-3.127540416000001</v>
+        <v>-9.613895104000003</v>
       </c>
       <c r="P64">
-        <v>-11.088552384</v>
+        <v>-34.08562809600001</v>
       </c>
       <c r="Q64">
-        <v>-1.588552383999996</v>
+        <v>-24.585628096</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.167285373976668</v>
+        <v>0.1747478708888031</v>
       </c>
       <c r="T64">
-        <v>1.583361678512776</v>
+        <v>1.680623029817204</v>
       </c>
       <c r="U64">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1786392221524569</v>
+        <v>0.1285257971560426</v>
       </c>
       <c r="W64">
-        <v>0.1205757621880193</v>
+        <v>0.1749920199310666</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.8119964643293497</v>
+        <v>0.5842081688911029</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6682,22 +6682,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1749016847854291</v>
+        <v>0.1764516847854291</v>
       </c>
       <c r="C65">
-        <v>-169.4325891966893</v>
+        <v>-181.5864308141958</v>
       </c>
       <c r="D65">
-        <v>324.1714108033107</v>
+        <v>320.3255691858043</v>
       </c>
       <c r="E65">
-        <v>413.304</v>
+        <v>421.6120000000001</v>
       </c>
       <c r="F65">
-        <v>523.404</v>
+        <v>531.7120000000001</v>
       </c>
       <c r="G65">
         <v>29.8</v>
@@ -6718,37 +6718,37 @@
         <v>61.4</v>
       </c>
       <c r="M65">
-        <v>105.0995232</v>
+        <v>106.7677696</v>
       </c>
       <c r="N65">
-        <v>-43.69952320000001</v>
+        <v>-45.36776960000002</v>
       </c>
       <c r="O65">
-        <v>-9.613895104000003</v>
+        <v>-9.980909312000005</v>
       </c>
       <c r="P65">
-        <v>-34.08562809600001</v>
+        <v>-35.38686028800002</v>
       </c>
       <c r="Q65">
-        <v>-24.585628096</v>
+        <v>-25.88686028800002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1747478708888031</v>
+        <v>0.1783297561912698</v>
       </c>
       <c r="T65">
-        <v>1.680623029817204</v>
+        <v>1.727307002867682</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1285257971560426</v>
+        <v>0.1265175815754795</v>
       </c>
       <c r="W65">
-        <v>0.1749920199310666</v>
+        <v>0.1753952696196437</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5842081688911029</v>
+        <v>0.5750799162521794</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6764,22 +6764,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1764516847854291</v>
+        <v>0.1780016847854291</v>
       </c>
       <c r="C66">
-        <v>-181.5864308141958</v>
+        <v>-193.6500912132583</v>
       </c>
       <c r="D66">
-        <v>320.3255691858043</v>
+        <v>316.5699087867417</v>
       </c>
       <c r="E66">
-        <v>421.6120000000001</v>
+        <v>429.9200000000001</v>
       </c>
       <c r="F66">
-        <v>531.7120000000001</v>
+        <v>540.0200000000001</v>
       </c>
       <c r="G66">
         <v>29.8</v>
@@ -6800,37 +6800,37 @@
         <v>61.4</v>
       </c>
       <c r="M66">
-        <v>106.7677696</v>
+        <v>108.436016</v>
       </c>
       <c r="N66">
-        <v>-45.36776960000002</v>
+        <v>-47.03601600000002</v>
       </c>
       <c r="O66">
-        <v>-9.980909312000005</v>
+        <v>-10.34792352000001</v>
       </c>
       <c r="P66">
-        <v>-35.38686028800002</v>
+        <v>-36.68809248000002</v>
       </c>
       <c r="Q66">
-        <v>-25.88686028800002</v>
+        <v>-27.18809248000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1783297561912698</v>
+        <v>0.1821163206538775</v>
       </c>
       <c r="T66">
-        <v>1.727307002867682</v>
+        <v>1.776658631521045</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1265175815754795</v>
+        <v>0.124571157243549</v>
       </c>
       <c r="W66">
-        <v>0.1753952696196437</v>
+        <v>0.1757861116254953</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5750799162521794</v>
+        <v>0.5662325329252228</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6846,22 +6846,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1780016847854291</v>
+        <v>0.1795516847854291</v>
       </c>
       <c r="C67">
-        <v>-193.6500912132583</v>
+        <v>-205.6267056266516</v>
       </c>
       <c r="D67">
-        <v>316.5699087867417</v>
+        <v>312.9012943733484</v>
       </c>
       <c r="E67">
-        <v>429.9200000000001</v>
+        <v>438.2280000000001</v>
       </c>
       <c r="F67">
-        <v>540.0200000000001</v>
+        <v>548.3280000000001</v>
       </c>
       <c r="G67">
         <v>29.8</v>
@@ -6882,37 +6882,37 @@
         <v>61.4</v>
       </c>
       <c r="M67">
-        <v>108.436016</v>
+        <v>110.1042624</v>
       </c>
       <c r="N67">
-        <v>-47.03601600000002</v>
+        <v>-48.70426240000003</v>
       </c>
       <c r="O67">
-        <v>-10.34792352000001</v>
+        <v>-10.71493772800001</v>
       </c>
       <c r="P67">
-        <v>-36.68809248000002</v>
+        <v>-37.98932467200002</v>
       </c>
       <c r="Q67">
-        <v>-27.18809248000002</v>
+        <v>-28.48932467200002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1821163206538775</v>
+        <v>0.186125624202521</v>
       </c>
       <c r="T67">
-        <v>1.776658631521045</v>
+        <v>1.828913297154017</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.124571157243549</v>
+        <v>0.1226837154671316</v>
       </c>
       <c r="W67">
-        <v>0.1757861116254953</v>
+        <v>0.1761651099342</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5662325329252228</v>
+        <v>0.5576532521233255</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6928,22 +6928,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1795516847854291</v>
+        <v>0.1811016847854291</v>
       </c>
       <c r="C68">
-        <v>-205.6267056266516</v>
+        <v>-217.5192656197354</v>
       </c>
       <c r="D68">
-        <v>312.9012943733484</v>
+        <v>309.3167343802647</v>
       </c>
       <c r="E68">
-        <v>438.2280000000001</v>
+        <v>446.5360000000001</v>
       </c>
       <c r="F68">
-        <v>548.3280000000001</v>
+        <v>556.6360000000001</v>
       </c>
       <c r="G68">
         <v>29.8</v>
@@ -6964,37 +6964,37 @@
         <v>61.4</v>
       </c>
       <c r="M68">
-        <v>110.1042624</v>
+        <v>111.7725088</v>
       </c>
       <c r="N68">
-        <v>-48.70426240000003</v>
+        <v>-50.37250880000003</v>
       </c>
       <c r="O68">
-        <v>-10.71493772800001</v>
+        <v>-11.08195193600001</v>
       </c>
       <c r="P68">
-        <v>-37.98932467200002</v>
+        <v>-39.29055686400002</v>
       </c>
       <c r="Q68">
-        <v>-28.48932467200002</v>
+        <v>-29.79055686400002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.186125624202521</v>
+        <v>0.1903779158450216</v>
       </c>
       <c r="T68">
-        <v>1.828913297154017</v>
+        <v>1.88433491221929</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1226837154671316</v>
+        <v>0.1208526152362789</v>
       </c>
       <c r="W68">
-        <v>0.1761651099342</v>
+        <v>0.1765327948605552</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5576532521233255</v>
+        <v>0.5493300692558132</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7010,22 +7010,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1811016847854291</v>
+        <v>0.1826516847854291</v>
       </c>
       <c r="C69">
-        <v>-217.5192656197354</v>
+        <v>-229.3306272264349</v>
       </c>
       <c r="D69">
-        <v>309.3167343802647</v>
+        <v>305.8133727735652</v>
       </c>
       <c r="E69">
-        <v>446.5360000000001</v>
+        <v>454.8440000000001</v>
       </c>
       <c r="F69">
-        <v>556.6360000000001</v>
+        <v>564.9440000000001</v>
       </c>
       <c r="G69">
         <v>29.8</v>
@@ -7046,37 +7046,37 @@
         <v>61.4</v>
       </c>
       <c r="M69">
-        <v>111.7725088</v>
+        <v>113.4407552</v>
       </c>
       <c r="N69">
-        <v>-50.37250880000003</v>
+        <v>-52.04075520000001</v>
       </c>
       <c r="O69">
-        <v>-11.08195193600001</v>
+        <v>-11.448966144</v>
       </c>
       <c r="P69">
-        <v>-39.29055686400002</v>
+        <v>-40.59178905600001</v>
       </c>
       <c r="Q69">
-        <v>-29.79055686400002</v>
+        <v>-31.091789056</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1903779158450216</v>
+        <v>0.1948959757151786</v>
       </c>
       <c r="T69">
-        <v>1.88433491221929</v>
+        <v>1.943220378226143</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1208526152362789</v>
+        <v>0.1190753708945689</v>
       </c>
       <c r="W69">
-        <v>0.1765327948605552</v>
+        <v>0.1768896655243706</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5493300692558132</v>
+        <v>0.5412516858844042</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7092,22 +7092,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1826516847854291</v>
+        <v>0.1842016847854291</v>
       </c>
       <c r="C70">
-        <v>-229.3306272264349</v>
+        <v>-241.0635185385162</v>
       </c>
       <c r="D70">
-        <v>305.8133727735652</v>
+        <v>302.3884814614839</v>
       </c>
       <c r="E70">
-        <v>454.8440000000001</v>
+        <v>463.152</v>
       </c>
       <c r="F70">
-        <v>564.9440000000001</v>
+        <v>573.2520000000001</v>
       </c>
       <c r="G70">
         <v>29.8</v>
@@ -7128,37 +7128,37 @@
         <v>61.4</v>
       </c>
       <c r="M70">
-        <v>113.4407552</v>
+        <v>115.1090016</v>
       </c>
       <c r="N70">
-        <v>-52.04075520000001</v>
+        <v>-53.70900160000001</v>
       </c>
       <c r="O70">
-        <v>-11.448966144</v>
+        <v>-11.815980352</v>
       </c>
       <c r="P70">
-        <v>-40.59178905600001</v>
+        <v>-41.89302124800001</v>
       </c>
       <c r="Q70">
-        <v>-31.091789056</v>
+        <v>-32.393021248</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1948959757151786</v>
+        <v>0.199705523318894</v>
       </c>
       <c r="T70">
-        <v>1.943220378226143</v>
+        <v>2.005904906556019</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1190753708945689</v>
+        <v>0.1173496408816042</v>
       </c>
       <c r="W70">
-        <v>0.1768896655243706</v>
+        <v>0.1772361921109739</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5412516858844042</v>
+        <v>0.5334074585527462</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7174,22 +7174,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1842016847854291</v>
+        <v>0.1857516847854291</v>
       </c>
       <c r="C71">
-        <v>-241.0635185385162</v>
+        <v>-252.7205467905441</v>
       </c>
       <c r="D71">
-        <v>302.3884814614839</v>
+        <v>299.039453209456</v>
       </c>
       <c r="E71">
-        <v>463.152</v>
+        <v>471.46</v>
       </c>
       <c r="F71">
-        <v>573.2520000000001</v>
+        <v>581.5600000000001</v>
       </c>
       <c r="G71">
         <v>29.8</v>
@@ -7210,37 +7210,37 @@
         <v>61.4</v>
       </c>
       <c r="M71">
-        <v>115.1090016</v>
+        <v>116.777248</v>
       </c>
       <c r="N71">
-        <v>-53.70900160000001</v>
+        <v>-55.37724800000002</v>
       </c>
       <c r="O71">
-        <v>-11.815980352</v>
+        <v>-12.18299456</v>
       </c>
       <c r="P71">
-        <v>-41.89302124800001</v>
+        <v>-43.19425344000001</v>
       </c>
       <c r="Q71">
-        <v>-32.393021248</v>
+        <v>-33.69425344</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.199705523318894</v>
+        <v>0.2048357074295238</v>
       </c>
       <c r="T71">
-        <v>2.005904906556019</v>
+        <v>2.072768403441219</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1173496408816042</v>
+        <v>0.1156732174404384</v>
       </c>
       <c r="W71">
-        <v>0.1772361921109739</v>
+        <v>0.17757281793796</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5334074585527462</v>
+        <v>0.5257873520019927</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7256,22 +7256,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1857516847854291</v>
+        <v>0.1873016847854291</v>
       </c>
       <c r="C72">
-        <v>-252.7205467905441</v>
+        <v>-264.3042049791905</v>
       </c>
       <c r="D72">
-        <v>299.039453209456</v>
+        <v>295.7637950208097</v>
       </c>
       <c r="E72">
-        <v>471.46</v>
+        <v>479.7680000000001</v>
       </c>
       <c r="F72">
-        <v>581.5600000000001</v>
+        <v>589.8680000000002</v>
       </c>
       <c r="G72">
         <v>29.8</v>
@@ -7292,37 +7292,37 @@
         <v>61.4</v>
       </c>
       <c r="M72">
-        <v>116.777248</v>
+        <v>118.4454944</v>
       </c>
       <c r="N72">
-        <v>-55.37724800000002</v>
+        <v>-57.04549440000005</v>
       </c>
       <c r="O72">
-        <v>-12.18299456</v>
+        <v>-12.55000876800001</v>
       </c>
       <c r="P72">
-        <v>-43.19425344000001</v>
+        <v>-44.49548563200003</v>
       </c>
       <c r="Q72">
-        <v>-33.69425344</v>
+        <v>-34.99548563200003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2048357074295238</v>
+        <v>0.2103196973408867</v>
       </c>
       <c r="T72">
-        <v>2.072768403441219</v>
+        <v>2.144243175973676</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1156732174404384</v>
+        <v>0.1140440171947984</v>
       </c>
       <c r="W72">
-        <v>0.17757281793796</v>
+        <v>0.1778999613472845</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5257873520019927</v>
+        <v>0.5183818963399927</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7338,22 +7338,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1873016847854291</v>
+        <v>0.1888516847854291</v>
       </c>
       <c r="C73">
-        <v>-264.3042049791904</v>
+        <v>-275.816878052212</v>
       </c>
       <c r="D73">
-        <v>295.7637950208097</v>
+        <v>292.559121947788</v>
       </c>
       <c r="E73">
-        <v>479.768</v>
+        <v>488.076</v>
       </c>
       <c r="F73">
-        <v>589.8680000000001</v>
+        <v>598.176</v>
       </c>
       <c r="G73">
         <v>29.8</v>
@@ -7374,37 +7374,37 @@
         <v>61.4</v>
       </c>
       <c r="M73">
-        <v>118.4454944</v>
+        <v>120.1137408</v>
       </c>
       <c r="N73">
-        <v>-57.04549440000002</v>
+        <v>-58.71374080000002</v>
       </c>
       <c r="O73">
-        <v>-12.550008768</v>
+        <v>-12.917022976</v>
       </c>
       <c r="P73">
-        <v>-44.49548563200001</v>
+        <v>-45.79671782400001</v>
       </c>
       <c r="Q73">
-        <v>-34.995485632</v>
+        <v>-36.29671782400001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2103196973408867</v>
+        <v>0.2161954008173469</v>
       </c>
       <c r="T73">
-        <v>2.144243175973675</v>
+        <v>2.220823289401306</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1140440171947984</v>
+        <v>0.1124600725115373</v>
       </c>
       <c r="W73">
-        <v>0.1778999613472845</v>
+        <v>0.1782180174396833</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5183818963399928</v>
+        <v>0.511182147779715</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7420,22 +7420,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1888516847854291</v>
+        <v>0.1904016847854291</v>
       </c>
       <c r="C74">
-        <v>-275.816878052212</v>
+        <v>-287.2608486993865</v>
       </c>
       <c r="D74">
-        <v>292.559121947788</v>
+        <v>289.4231513006135</v>
       </c>
       <c r="E74">
-        <v>488.076</v>
+        <v>496.384</v>
       </c>
       <c r="F74">
-        <v>598.176</v>
+        <v>606.484</v>
       </c>
       <c r="G74">
         <v>29.8</v>
@@ -7456,37 +7456,37 @@
         <v>61.4</v>
       </c>
       <c r="M74">
-        <v>120.1137408</v>
+        <v>121.7819872</v>
       </c>
       <c r="N74">
-        <v>-58.71374080000002</v>
+        <v>-60.38198720000002</v>
       </c>
       <c r="O74">
-        <v>-12.917022976</v>
+        <v>-13.284037184</v>
       </c>
       <c r="P74">
-        <v>-45.79671782400001</v>
+        <v>-47.09795001600001</v>
       </c>
       <c r="Q74">
-        <v>-36.29671782400001</v>
+        <v>-37.59795001600001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2161954008173469</v>
+        <v>0.2225063415883597</v>
       </c>
       <c r="T74">
-        <v>2.220823289401306</v>
+        <v>2.303076003823576</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1124600725115373</v>
+        <v>0.1109195235730231</v>
       </c>
       <c r="W74">
-        <v>0.1782180174396833</v>
+        <v>0.178527359666537</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.511182147779715</v>
+        <v>0.5041796526046505</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7502,22 +7502,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1904016847854291</v>
+        <v>0.2184756234548023</v>
       </c>
       <c r="C75">
-        <v>-287.2608486993865</v>
+        <v>-342.6238274887749</v>
       </c>
       <c r="D75">
-        <v>289.4231513006135</v>
+        <v>242.3681725112251</v>
       </c>
       <c r="E75">
-        <v>496.384</v>
+        <v>504.692</v>
       </c>
       <c r="F75">
-        <v>606.484</v>
+        <v>614.792</v>
       </c>
       <c r="G75">
         <v>29.8</v>
@@ -7538,45 +7538,45 @@
         <v>61.4</v>
       </c>
       <c r="M75">
-        <v>121.7819872</v>
+        <v>144.9679536</v>
       </c>
       <c r="N75">
-        <v>-60.38198720000002</v>
+        <v>-83.56795360000001</v>
       </c>
       <c r="O75">
-        <v>-13.284037184</v>
+        <v>-18.384949792</v>
       </c>
       <c r="P75">
-        <v>-47.09795001600001</v>
+        <v>-65.18300380800001</v>
       </c>
       <c r="Q75">
-        <v>-37.59795001600001</v>
+        <v>-55.683003808</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2225063415883597</v>
+        <v>0.2317025034547319</v>
       </c>
       <c r="T75">
-        <v>2.303076003823576</v>
+        <v>2.422932821249275</v>
       </c>
       <c r="U75">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1109195235730231</v>
+        <v>0.09317921419565378</v>
       </c>
       <c r="W75">
-        <v>0.178527359666537</v>
+        <v>0.2138283412926648</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.5041796526046505</v>
+        <v>0.4235418827075172</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7584,22 +7584,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2184756234548023</v>
+        <v>0.2203756234548023</v>
       </c>
       <c r="C76">
-        <v>-342.6238274887749</v>
+        <v>-353.5696501048891</v>
       </c>
       <c r="D76">
-        <v>242.3681725112251</v>
+        <v>239.7303498951109</v>
       </c>
       <c r="E76">
-        <v>504.692</v>
+        <v>513</v>
       </c>
       <c r="F76">
-        <v>614.792</v>
+        <v>623.1</v>
       </c>
       <c r="G76">
         <v>29.8</v>
@@ -7620,37 +7620,37 @@
         <v>61.4</v>
       </c>
       <c r="M76">
-        <v>144.9679536</v>
+        <v>146.92698</v>
       </c>
       <c r="N76">
-        <v>-83.56795360000001</v>
+        <v>-85.52698000000001</v>
       </c>
       <c r="O76">
-        <v>-18.384949792</v>
+        <v>-18.8159356</v>
       </c>
       <c r="P76">
-        <v>-65.18300380800001</v>
+        <v>-66.71104440000001</v>
       </c>
       <c r="Q76">
-        <v>-55.683003808</v>
+        <v>-57.2110444</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2317025034547319</v>
+        <v>0.2391386035929212</v>
       </c>
       <c r="T76">
-        <v>2.422932821249275</v>
+        <v>2.519850134099246</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09317921419565378</v>
+        <v>0.09193682467304506</v>
       </c>
       <c r="W76">
-        <v>0.2138283412926648</v>
+        <v>0.214121296742096</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4235418827075172</v>
+        <v>0.4178946576047503</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7666,22 +7666,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2203756234548023</v>
+        <v>0.2222756234548023</v>
       </c>
       <c r="C77">
-        <v>-353.5696501048891</v>
+        <v>-364.4586732279913</v>
       </c>
       <c r="D77">
-        <v>239.7303498951109</v>
+        <v>237.1493267720087</v>
       </c>
       <c r="E77">
-        <v>513</v>
+        <v>521.308</v>
       </c>
       <c r="F77">
-        <v>623.1</v>
+        <v>631.408</v>
       </c>
       <c r="G77">
         <v>29.8</v>
@@ -7702,37 +7702,37 @@
         <v>61.4</v>
       </c>
       <c r="M77">
-        <v>146.92698</v>
+        <v>148.8860064</v>
       </c>
       <c r="N77">
-        <v>-85.52698000000001</v>
+        <v>-87.48600640000001</v>
       </c>
       <c r="O77">
-        <v>-18.8159356</v>
+        <v>-19.246921408</v>
       </c>
       <c r="P77">
-        <v>-66.71104440000001</v>
+        <v>-68.239084992</v>
       </c>
       <c r="Q77">
-        <v>-57.2110444</v>
+        <v>-58.739084992</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2391386035929212</v>
+        <v>0.2471943787426263</v>
       </c>
       <c r="T77">
-        <v>2.519850134099246</v>
+        <v>2.624843889686715</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09193682467304506</v>
+        <v>0.09072712961155763</v>
       </c>
       <c r="W77">
-        <v>0.214121296742096</v>
+        <v>0.2144065428375947</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4178946576047503</v>
+        <v>0.4123960436888984</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7748,22 +7748,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2222756234548023</v>
+        <v>0.2241756234548022</v>
       </c>
       <c r="C78">
-        <v>-364.4586732279913</v>
+        <v>-375.2927118880943</v>
       </c>
       <c r="D78">
-        <v>237.1493267720087</v>
+        <v>234.6232881119058</v>
       </c>
       <c r="E78">
-        <v>521.308</v>
+        <v>529.6160000000001</v>
       </c>
       <c r="F78">
-        <v>631.408</v>
+        <v>639.7160000000001</v>
       </c>
       <c r="G78">
         <v>29.8</v>
@@ -7784,37 +7784,37 @@
         <v>61.4</v>
       </c>
       <c r="M78">
-        <v>148.8860064</v>
+        <v>150.8450328</v>
       </c>
       <c r="N78">
-        <v>-87.48600640000001</v>
+        <v>-89.44503280000004</v>
       </c>
       <c r="O78">
-        <v>-19.246921408</v>
+        <v>-19.67790721600001</v>
       </c>
       <c r="P78">
-        <v>-68.239084992</v>
+        <v>-69.76712558400003</v>
       </c>
       <c r="Q78">
-        <v>-58.739084992</v>
+        <v>-60.26712558400002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2471943787426263</v>
+        <v>0.2559506560792621</v>
       </c>
       <c r="T78">
-        <v>2.624843889686715</v>
+        <v>2.738967537064398</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09072712961155763</v>
+        <v>0.08954885520101791</v>
       </c>
       <c r="W78">
-        <v>0.2144065428375947</v>
+        <v>0.2146843799436</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4123960436888984</v>
+        <v>0.4070402509137178</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7830,22 +7830,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2241756234548022</v>
+        <v>0.2260756234548023</v>
       </c>
       <c r="C79">
-        <v>-375.2927118880943</v>
+        <v>-386.0735045977775</v>
       </c>
       <c r="D79">
-        <v>234.6232881119058</v>
+        <v>232.1504954022226</v>
       </c>
       <c r="E79">
-        <v>529.6160000000001</v>
+        <v>537.9240000000001</v>
       </c>
       <c r="F79">
-        <v>639.7160000000001</v>
+        <v>648.0240000000001</v>
       </c>
       <c r="G79">
         <v>29.8</v>
@@ -7866,37 +7866,37 @@
         <v>61.4</v>
       </c>
       <c r="M79">
-        <v>150.8450328</v>
+        <v>152.8040592</v>
       </c>
       <c r="N79">
-        <v>-89.44503280000004</v>
+        <v>-91.40405920000003</v>
       </c>
       <c r="O79">
-        <v>-19.67790721600001</v>
+        <v>-20.10889302400001</v>
       </c>
       <c r="P79">
-        <v>-69.76712558400003</v>
+        <v>-71.29516617600002</v>
       </c>
       <c r="Q79">
-        <v>-60.26712558400002</v>
+        <v>-61.79516617600002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2559506560792621</v>
+        <v>0.2655029586283195</v>
       </c>
       <c r="T79">
-        <v>2.738967537064398</v>
+        <v>2.863466061476416</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08954885520101791</v>
+        <v>0.08840079295485101</v>
       </c>
       <c r="W79">
-        <v>0.2146843799436</v>
+        <v>0.2149550930212461</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4070402509137178</v>
+        <v>0.4018217861584137</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7912,22 +7912,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2260756234548023</v>
+        <v>0.2279756234548023</v>
       </c>
       <c r="C80">
-        <v>-386.0735045977775</v>
+        <v>-396.8027173423777</v>
       </c>
       <c r="D80">
-        <v>232.1504954022226</v>
+        <v>229.7292826576224</v>
       </c>
       <c r="E80">
-        <v>537.9240000000001</v>
+        <v>546.2320000000001</v>
       </c>
       <c r="F80">
-        <v>648.0240000000001</v>
+        <v>656.3320000000001</v>
       </c>
       <c r="G80">
         <v>29.8</v>
@@ -7948,37 +7948,37 @@
         <v>61.4</v>
       </c>
       <c r="M80">
-        <v>152.8040592</v>
+        <v>154.7630856</v>
       </c>
       <c r="N80">
-        <v>-91.40405920000003</v>
+        <v>-93.36308560000003</v>
       </c>
       <c r="O80">
-        <v>-20.10889302400001</v>
+        <v>-20.53987883200001</v>
       </c>
       <c r="P80">
-        <v>-71.29516617600002</v>
+        <v>-72.82320676800003</v>
       </c>
       <c r="Q80">
-        <v>-61.79516617600002</v>
+        <v>-63.32320676800003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2655029586283195</v>
+        <v>0.2759650042772872</v>
       </c>
       <c r="T80">
-        <v>2.863466061476416</v>
+        <v>2.999821588213389</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08840079295485101</v>
+        <v>0.08728179557567568</v>
       </c>
       <c r="W80">
-        <v>0.2149550930212461</v>
+        <v>0.2152189526032557</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4018217861584137</v>
+        <v>0.3967354344348895</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7994,22 +7994,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2279756234548023</v>
+        <v>0.2298756234548023</v>
       </c>
       <c r="C81">
-        <v>-396.8027173423777</v>
+        <v>-407.4819473230635</v>
       </c>
       <c r="D81">
-        <v>229.7292826576224</v>
+        <v>227.3580526769366</v>
       </c>
       <c r="E81">
-        <v>546.2320000000001</v>
+        <v>554.5400000000001</v>
       </c>
       <c r="F81">
-        <v>656.3320000000001</v>
+        <v>664.6400000000001</v>
       </c>
       <c r="G81">
         <v>29.8</v>
@@ -8030,37 +8030,37 @@
         <v>61.4</v>
       </c>
       <c r="M81">
-        <v>154.7630856</v>
+        <v>156.722112</v>
       </c>
       <c r="N81">
-        <v>-93.36308560000003</v>
+        <v>-95.32211200000003</v>
       </c>
       <c r="O81">
-        <v>-20.53987883200001</v>
+        <v>-20.97086464000001</v>
       </c>
       <c r="P81">
-        <v>-72.82320676800003</v>
+        <v>-74.35124736000003</v>
       </c>
       <c r="Q81">
-        <v>-63.32320676800003</v>
+        <v>-64.85124736000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2759650042772872</v>
+        <v>0.2874732544911515</v>
       </c>
       <c r="T81">
-        <v>2.999821588213389</v>
+        <v>3.149812667624059</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08728179557567568</v>
+        <v>0.08619077313097974</v>
       </c>
       <c r="W81">
-        <v>0.2152189526032557</v>
+        <v>0.215476215695715</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3967354344348895</v>
+        <v>0.3917762415044533</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8076,22 +8076,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2298756234548023</v>
+        <v>0.2317756234548023</v>
       </c>
       <c r="C82">
-        <v>-407.4819473230635</v>
+        <v>-418.1127264704671</v>
       </c>
       <c r="D82">
-        <v>227.3580526769366</v>
+        <v>225.035273529533</v>
       </c>
       <c r="E82">
-        <v>554.5400000000001</v>
+        <v>562.8480000000001</v>
       </c>
       <c r="F82">
-        <v>664.6400000000001</v>
+        <v>672.9480000000001</v>
       </c>
       <c r="G82">
         <v>29.8</v>
@@ -8112,37 +8112,37 @@
         <v>61.4</v>
       </c>
       <c r="M82">
-        <v>156.722112</v>
+        <v>158.6811384</v>
       </c>
       <c r="N82">
-        <v>-95.32211200000003</v>
+        <v>-97.28113840000003</v>
       </c>
       <c r="O82">
-        <v>-20.97086464000001</v>
+        <v>-21.40185044800001</v>
       </c>
       <c r="P82">
-        <v>-74.35124736000003</v>
+        <v>-75.87928795200003</v>
       </c>
       <c r="Q82">
-        <v>-64.85124736000003</v>
+        <v>-66.37928795200003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2874732544911515</v>
+        <v>0.30019289946437</v>
       </c>
       <c r="T82">
-        <v>3.149812667624059</v>
+        <v>3.315592281709535</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08619077313097974</v>
+        <v>0.08512668951207875</v>
       </c>
       <c r="W82">
-        <v>0.215476215695715</v>
+        <v>0.2157271266130518</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3917762415044533</v>
+        <v>0.3869394977821762</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8158,22 +8158,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2317756234548023</v>
+        <v>0.2336756234548023</v>
       </c>
       <c r="C83">
-        <v>-418.1127264704671</v>
+        <v>-428.6965247451111</v>
       </c>
       <c r="D83">
-        <v>225.035273529533</v>
+        <v>222.759475254889</v>
       </c>
       <c r="E83">
-        <v>562.8480000000001</v>
+        <v>571.1560000000001</v>
       </c>
       <c r="F83">
-        <v>672.9480000000001</v>
+        <v>681.2560000000001</v>
       </c>
       <c r="G83">
         <v>29.8</v>
@@ -8194,37 +8194,37 @@
         <v>61.4</v>
       </c>
       <c r="M83">
-        <v>158.6811384</v>
+        <v>160.6401648</v>
       </c>
       <c r="N83">
-        <v>-97.28113840000003</v>
+        <v>-99.24016480000003</v>
       </c>
       <c r="O83">
-        <v>-21.40185044800001</v>
+        <v>-21.83283625600001</v>
       </c>
       <c r="P83">
-        <v>-75.87928795200003</v>
+        <v>-77.40732854400002</v>
       </c>
       <c r="Q83">
-        <v>-66.37928795200003</v>
+        <v>-67.90732854400002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.30019289946437</v>
+        <v>0.3143258383235017</v>
       </c>
       <c r="T83">
-        <v>3.315592281709535</v>
+        <v>3.499791852915621</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08512668951207875</v>
+        <v>0.08408855915217536</v>
       </c>
       <c r="W83">
-        <v>0.2157271266130518</v>
+        <v>0.215971917751917</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3869394977821762</v>
+        <v>0.3822207234189789</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8240,22 +8240,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2336756234548023</v>
+        <v>0.2355756234548023</v>
       </c>
       <c r="C84">
-        <v>-428.6965247451111</v>
+        <v>-439.2347532395789</v>
       </c>
       <c r="D84">
-        <v>222.759475254889</v>
+        <v>220.5292467604212</v>
       </c>
       <c r="E84">
-        <v>571.1560000000001</v>
+        <v>579.4640000000001</v>
       </c>
       <c r="F84">
-        <v>681.2560000000001</v>
+        <v>689.5640000000001</v>
       </c>
       <c r="G84">
         <v>29.8</v>
@@ -8276,37 +8276,37 @@
         <v>61.4</v>
       </c>
       <c r="M84">
-        <v>160.6401648</v>
+        <v>162.5991912</v>
       </c>
       <c r="N84">
-        <v>-99.24016480000003</v>
+        <v>-101.1991912</v>
       </c>
       <c r="O84">
-        <v>-21.83283625600001</v>
+        <v>-22.26382206400001</v>
       </c>
       <c r="P84">
-        <v>-77.40732854400002</v>
+        <v>-78.93536913600002</v>
       </c>
       <c r="Q84">
-        <v>-67.90732854400002</v>
+        <v>-69.43536913600002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3143258383235017</v>
+        <v>0.330121475871943</v>
       </c>
       <c r="T84">
-        <v>3.499791852915621</v>
+        <v>3.705661961910657</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08408855915217536</v>
+        <v>0.08307544398166722</v>
       </c>
       <c r="W84">
-        <v>0.215971917751917</v>
+        <v>0.2162108103091229</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3822207234189789</v>
+        <v>0.3776156544621238</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8322,22 +8322,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2355756234548023</v>
+        <v>0.2374756234548023</v>
       </c>
       <c r="C85">
-        <v>-439.2347532395789</v>
+        <v>-449.7287670961796</v>
       </c>
       <c r="D85">
-        <v>220.5292467604212</v>
+        <v>218.3432329038205</v>
       </c>
       <c r="E85">
-        <v>579.4640000000001</v>
+        <v>587.772</v>
       </c>
       <c r="F85">
-        <v>689.5640000000001</v>
+        <v>697.8720000000001</v>
       </c>
       <c r="G85">
         <v>29.8</v>
@@ -8358,37 +8358,37 @@
         <v>61.4</v>
       </c>
       <c r="M85">
-        <v>162.5991912</v>
+        <v>164.5582176</v>
       </c>
       <c r="N85">
-        <v>-101.1991912</v>
+        <v>-103.1582176</v>
       </c>
       <c r="O85">
-        <v>-22.26382206400001</v>
+        <v>-22.69480787200001</v>
       </c>
       <c r="P85">
-        <v>-78.93536913600002</v>
+        <v>-80.46340972800002</v>
       </c>
       <c r="Q85">
-        <v>-69.43536913600002</v>
+        <v>-70.96340972800002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.330121475871943</v>
+        <v>0.3478915681139395</v>
       </c>
       <c r="T85">
-        <v>3.705661961910657</v>
+        <v>3.937265834530074</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08307544398166722</v>
+        <v>0.08208645060093309</v>
       </c>
       <c r="W85">
-        <v>0.2162108103091229</v>
+        <v>0.2164440149483</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3776156544621238</v>
+        <v>0.3731202300042413</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8404,22 +8404,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2374756234548023</v>
+        <v>0.2393756234548023</v>
       </c>
       <c r="C86">
-        <v>-449.7287670961796</v>
+        <v>-460.1798682527885</v>
       </c>
       <c r="D86">
-        <v>218.3432329038205</v>
+        <v>216.2001317472115</v>
       </c>
       <c r="E86">
-        <v>587.772</v>
+        <v>596.08</v>
       </c>
       <c r="F86">
-        <v>697.8720000000001</v>
+        <v>706.1800000000001</v>
       </c>
       <c r="G86">
         <v>29.8</v>
@@ -8440,37 +8440,37 @@
         <v>61.4</v>
       </c>
       <c r="M86">
-        <v>164.5582176</v>
+        <v>166.517244</v>
       </c>
       <c r="N86">
-        <v>-103.1582176</v>
+        <v>-105.117244</v>
       </c>
       <c r="O86">
-        <v>-22.69480787200001</v>
+        <v>-23.12579368</v>
       </c>
       <c r="P86">
-        <v>-80.46340972800002</v>
+        <v>-81.99145032000003</v>
       </c>
       <c r="Q86">
-        <v>-70.96340972800002</v>
+        <v>-72.49145032000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3478915681139393</v>
+        <v>0.3680310059882019</v>
       </c>
       <c r="T86">
-        <v>3.937265834530072</v>
+        <v>4.199750223498743</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08208645060093309</v>
+        <v>0.08112072765268681</v>
       </c>
       <c r="W86">
-        <v>0.2164440149483</v>
+        <v>0.2166717324194964</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3731202300042413</v>
+        <v>0.3687305802394856</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8486,22 +8486,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2393756234548023</v>
+        <v>0.2412756234548023</v>
       </c>
       <c r="C87">
-        <v>-460.1798682527885</v>
+        <v>-470.58930802855</v>
       </c>
       <c r="D87">
-        <v>216.2001317472115</v>
+        <v>214.0986919714501</v>
       </c>
       <c r="E87">
-        <v>596.08</v>
+        <v>604.388</v>
       </c>
       <c r="F87">
-        <v>706.1800000000001</v>
+        <v>714.4880000000001</v>
       </c>
       <c r="G87">
         <v>29.8</v>
@@ -8522,37 +8522,37 @@
         <v>61.4</v>
       </c>
       <c r="M87">
-        <v>166.517244</v>
+        <v>168.4762704</v>
       </c>
       <c r="N87">
-        <v>-105.117244</v>
+        <v>-107.0762704</v>
       </c>
       <c r="O87">
-        <v>-23.12579368</v>
+        <v>-23.55677948800001</v>
       </c>
       <c r="P87">
-        <v>-81.99145032000003</v>
+        <v>-83.51949091200002</v>
       </c>
       <c r="Q87">
-        <v>-72.49145032000001</v>
+        <v>-74.01949091200001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3680310059882019</v>
+        <v>0.3910475064159306</v>
       </c>
       <c r="T87">
-        <v>4.199750223498743</v>
+        <v>4.499732382320082</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08112072765268681</v>
+        <v>0.08017746337765556</v>
       </c>
       <c r="W87">
-        <v>0.2166717324194964</v>
+        <v>0.2168941541355488</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3687305802394856</v>
+        <v>0.3644430153529798</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8568,22 +8568,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2412756234548023</v>
+        <v>0.2431756234548023</v>
       </c>
       <c r="C88">
-        <v>-470.58930802855</v>
+        <v>-480.9582895602381</v>
       </c>
       <c r="D88">
-        <v>214.0986919714501</v>
+        <v>212.037710439762</v>
       </c>
       <c r="E88">
-        <v>604.388</v>
+        <v>612.696</v>
       </c>
       <c r="F88">
-        <v>714.4880000000001</v>
+        <v>722.796</v>
       </c>
       <c r="G88">
         <v>29.8</v>
@@ -8604,37 +8604,37 @@
         <v>61.4</v>
       </c>
       <c r="M88">
-        <v>168.4762704</v>
+        <v>170.4352968</v>
       </c>
       <c r="N88">
-        <v>-107.0762704</v>
+        <v>-109.0352968</v>
       </c>
       <c r="O88">
-        <v>-23.55677948800001</v>
+        <v>-23.98776529600001</v>
       </c>
       <c r="P88">
-        <v>-83.51949091200002</v>
+        <v>-85.04753150400002</v>
       </c>
       <c r="Q88">
-        <v>-74.01949091200001</v>
+        <v>-75.54753150400001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3910475064159306</v>
+        <v>0.4176050069094638</v>
       </c>
       <c r="T88">
-        <v>4.499732382320082</v>
+        <v>4.84586564249855</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08017746337765556</v>
+        <v>0.07925588333883195</v>
       </c>
       <c r="W88">
-        <v>0.2168941541355488</v>
+        <v>0.2171114627087034</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3644430153529798</v>
+        <v>0.3602540151765089</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8650,22 +8650,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2431756234548023</v>
+        <v>0.2450756234548023</v>
       </c>
       <c r="C89">
-        <v>-480.9582895602381</v>
+        <v>-491.2879700992373</v>
       </c>
       <c r="D89">
-        <v>212.037710439762</v>
+        <v>210.0160299007627</v>
       </c>
       <c r="E89">
-        <v>612.696</v>
+        <v>621.004</v>
       </c>
       <c r="F89">
-        <v>722.796</v>
+        <v>731.104</v>
       </c>
       <c r="G89">
         <v>29.8</v>
@@ -8686,37 +8686,37 @@
         <v>61.4</v>
       </c>
       <c r="M89">
-        <v>170.4352968</v>
+        <v>172.3943232</v>
       </c>
       <c r="N89">
-        <v>-109.0352968</v>
+        <v>-110.9943232</v>
       </c>
       <c r="O89">
-        <v>-23.98776529600001</v>
+        <v>-24.41875110400001</v>
       </c>
       <c r="P89">
-        <v>-85.04753150400002</v>
+        <v>-86.57557209600002</v>
       </c>
       <c r="Q89">
-        <v>-75.54753150400001</v>
+        <v>-77.075572096</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4176050069094638</v>
+        <v>0.4485887574852525</v>
       </c>
       <c r="T89">
-        <v>4.84586564249855</v>
+        <v>5.24968777937343</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07925588333883195</v>
+        <v>0.07835524830089068</v>
       </c>
       <c r="W89">
-        <v>0.2171114627087034</v>
+        <v>0.21732383245065</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3602540151765089</v>
+        <v>0.3561602195495031</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8732,22 +8732,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2450756234548023</v>
+        <v>0.2469756234548023</v>
       </c>
       <c r="C90">
-        <v>-491.2879700992373</v>
+        <v>-501.5794631783634</v>
       </c>
       <c r="D90">
-        <v>210.0160299007627</v>
+        <v>208.0325368216366</v>
       </c>
       <c r="E90">
-        <v>621.004</v>
+        <v>629.312</v>
       </c>
       <c r="F90">
-        <v>731.104</v>
+        <v>739.412</v>
       </c>
       <c r="G90">
         <v>29.8</v>
@@ -8768,37 +8768,37 @@
         <v>61.4</v>
       </c>
       <c r="M90">
-        <v>172.3943232</v>
+        <v>174.3533496</v>
       </c>
       <c r="N90">
-        <v>-110.9943232</v>
+        <v>-112.9533496</v>
       </c>
       <c r="O90">
-        <v>-24.41875110400001</v>
+        <v>-24.849736912</v>
       </c>
       <c r="P90">
-        <v>-86.57557209600002</v>
+        <v>-88.103612688</v>
       </c>
       <c r="Q90">
-        <v>-77.075572096</v>
+        <v>-78.603612688</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4485887574852525</v>
+        <v>0.485205917256639</v>
       </c>
       <c r="T90">
-        <v>5.24968777937343</v>
+        <v>5.726932122952832</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07835524830089068</v>
+        <v>0.07747485225256606</v>
       </c>
       <c r="W90">
-        <v>0.21732383245065</v>
+        <v>0.2175314298388449</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3561602195495031</v>
+        <v>0.3521584193298458</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8814,22 +8814,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2469756234548023</v>
+        <v>0.2488756234548023</v>
       </c>
       <c r="C91">
-        <v>-501.5794631783634</v>
+        <v>-511.8338406570423</v>
       </c>
       <c r="D91">
-        <v>208.0325368216366</v>
+        <v>206.0861593429578</v>
       </c>
       <c r="E91">
-        <v>629.312</v>
+        <v>637.62</v>
       </c>
       <c r="F91">
-        <v>739.412</v>
+        <v>747.72</v>
       </c>
       <c r="G91">
         <v>29.8</v>
@@ -8850,37 +8850,37 @@
         <v>61.4</v>
       </c>
       <c r="M91">
-        <v>174.3533496</v>
+        <v>176.312376</v>
       </c>
       <c r="N91">
-        <v>-112.9533496</v>
+        <v>-114.912376</v>
       </c>
       <c r="O91">
-        <v>-24.849736912</v>
+        <v>-25.28072272</v>
       </c>
       <c r="P91">
-        <v>-88.103612688</v>
+        <v>-89.63165327999999</v>
       </c>
       <c r="Q91">
-        <v>-78.603612688</v>
+        <v>-80.13165327999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.485205917256639</v>
+        <v>0.529146508982303</v>
       </c>
       <c r="T91">
-        <v>5.726932122952832</v>
+        <v>6.299625335248117</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07747485225256606</v>
+        <v>0.0766140205608709</v>
       </c>
       <c r="W91">
-        <v>0.2175314298388449</v>
+        <v>0.2177344139517467</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3521584193298458</v>
+        <v>0.3482455480039587</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8896,22 +8896,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2488756234548023</v>
+        <v>0.2507756234548023</v>
       </c>
       <c r="C92">
-        <v>-511.8338406570423</v>
+        <v>-522.0521346527474</v>
       </c>
       <c r="D92">
-        <v>206.0861593429578</v>
+        <v>204.1758653472527</v>
       </c>
       <c r="E92">
-        <v>637.62</v>
+        <v>645.9280000000001</v>
       </c>
       <c r="F92">
-        <v>747.72</v>
+        <v>756.0280000000001</v>
       </c>
       <c r="G92">
         <v>29.8</v>
@@ -8932,37 +8932,37 @@
         <v>61.4</v>
       </c>
       <c r="M92">
-        <v>176.312376</v>
+        <v>178.2714024</v>
       </c>
       <c r="N92">
-        <v>-114.912376</v>
+        <v>-116.8714024</v>
       </c>
       <c r="O92">
-        <v>-25.28072272</v>
+        <v>-25.71170852800001</v>
       </c>
       <c r="P92">
-        <v>-89.63165327999999</v>
+        <v>-91.15969387200002</v>
       </c>
       <c r="Q92">
-        <v>-80.13165327999999</v>
+        <v>-81.65969387200002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.529146508982303</v>
+        <v>0.5828516766470034</v>
       </c>
       <c r="T92">
-        <v>6.299625335248117</v>
+        <v>6.999583705831242</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0766140205608709</v>
+        <v>0.07577210824701516</v>
       </c>
       <c r="W92">
-        <v>0.2177344139517467</v>
+        <v>0.2179329368753538</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3482455480039587</v>
+        <v>0.344418673850069</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8978,22 +8978,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2507756234548023</v>
+        <v>0.2526756234548023</v>
       </c>
       <c r="C93">
-        <v>-522.0521346527474</v>
+        <v>-532.2353393660013</v>
       </c>
       <c r="D93">
-        <v>204.1758653472527</v>
+        <v>202.3006606339988</v>
       </c>
       <c r="E93">
-        <v>645.9280000000001</v>
+        <v>654.2360000000001</v>
       </c>
       <c r="F93">
-        <v>756.0280000000001</v>
+        <v>764.3360000000001</v>
       </c>
       <c r="G93">
         <v>29.8</v>
@@ -9014,37 +9014,37 @@
         <v>61.4</v>
       </c>
       <c r="M93">
-        <v>178.2714024</v>
+        <v>180.2304288</v>
       </c>
       <c r="N93">
-        <v>-116.8714024</v>
+        <v>-118.8304288</v>
       </c>
       <c r="O93">
-        <v>-25.71170852800001</v>
+        <v>-26.14269433600001</v>
       </c>
       <c r="P93">
-        <v>-91.15969387200002</v>
+        <v>-92.68773446400002</v>
       </c>
       <c r="Q93">
-        <v>-81.65969387200002</v>
+        <v>-83.18773446400002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5828516766470034</v>
+        <v>0.6499831362278788</v>
       </c>
       <c r="T93">
-        <v>6.999583705831242</v>
+        <v>7.874531669060148</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07577210824701516</v>
+        <v>0.074948498374765</v>
       </c>
       <c r="W93">
-        <v>0.2179329368753538</v>
+        <v>0.2181271440832304</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.344418673850069</v>
+        <v>0.3406749926125682</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9060,22 +9060,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2526756234548023</v>
+        <v>0.2545756234548023</v>
       </c>
       <c r="C94">
-        <v>-532.2353393660013</v>
+        <v>-542.3844128057259</v>
       </c>
       <c r="D94">
-        <v>202.3006606339988</v>
+        <v>200.4595871942742</v>
       </c>
       <c r="E94">
-        <v>654.2360000000001</v>
+        <v>662.5440000000001</v>
       </c>
       <c r="F94">
-        <v>764.3360000000001</v>
+        <v>772.6440000000001</v>
       </c>
       <c r="G94">
         <v>29.8</v>
@@ -9096,37 +9096,37 @@
         <v>61.4</v>
       </c>
       <c r="M94">
-        <v>180.2304288</v>
+        <v>182.1894552</v>
       </c>
       <c r="N94">
-        <v>-118.8304288</v>
+        <v>-120.7894552</v>
       </c>
       <c r="O94">
-        <v>-26.14269433600001</v>
+        <v>-26.573680144</v>
       </c>
       <c r="P94">
-        <v>-92.68773446400002</v>
+        <v>-94.21577505600001</v>
       </c>
       <c r="Q94">
-        <v>-83.18773446400002</v>
+        <v>-84.71577505600001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6499831362278788</v>
+        <v>0.7362950128318617</v>
       </c>
       <c r="T94">
-        <v>7.874531669060148</v>
+        <v>8.999464764640171</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.074948498374765</v>
+        <v>0.07414260054277827</v>
       </c>
       <c r="W94">
-        <v>0.2181271440832304</v>
+        <v>0.2183171747920129</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3406749926125682</v>
+        <v>0.3370118206489922</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9142,22 +9142,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2545756234548023</v>
+        <v>0.2564756234548023</v>
       </c>
       <c r="C95">
-        <v>-542.3844128057259</v>
+        <v>-552.5002784212314</v>
       </c>
       <c r="D95">
-        <v>200.4595871942742</v>
+        <v>198.6517215787686</v>
       </c>
       <c r="E95">
-        <v>662.5440000000001</v>
+        <v>670.8520000000001</v>
       </c>
       <c r="F95">
-        <v>772.6440000000001</v>
+        <v>780.9520000000001</v>
       </c>
       <c r="G95">
         <v>29.8</v>
@@ -9178,37 +9178,37 @@
         <v>61.4</v>
       </c>
       <c r="M95">
-        <v>182.1894552</v>
+        <v>184.1484816</v>
       </c>
       <c r="N95">
-        <v>-120.7894552</v>
+        <v>-122.7484816</v>
       </c>
       <c r="O95">
-        <v>-26.573680144</v>
+        <v>-27.004665952</v>
       </c>
       <c r="P95">
-        <v>-94.21577505600001</v>
+        <v>-95.74381564800001</v>
       </c>
       <c r="Q95">
-        <v>-84.71577505600001</v>
+        <v>-86.24381564800001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7362950128318617</v>
+        <v>0.8513775149705055</v>
       </c>
       <c r="T95">
-        <v>8.999464764640171</v>
+        <v>10.49937555874687</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07414260054277827</v>
+        <v>0.07335384947317425</v>
       </c>
       <c r="W95">
-        <v>0.2183171747920129</v>
+        <v>0.2185031622942255</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3370118206489922</v>
+        <v>0.3334265885144284</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9224,22 +9224,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2564756234548023</v>
+        <v>0.2583756234548023</v>
       </c>
       <c r="C96">
-        <v>-552.5002784212314</v>
+        <v>-562.5838266466841</v>
       </c>
       <c r="D96">
-        <v>198.6517215787686</v>
+        <v>196.876173353316</v>
       </c>
       <c r="E96">
-        <v>670.8520000000001</v>
+        <v>679.1600000000001</v>
       </c>
       <c r="F96">
-        <v>780.9520000000001</v>
+        <v>789.2600000000001</v>
       </c>
       <c r="G96">
         <v>29.8</v>
@@ -9260,37 +9260,37 @@
         <v>61.4</v>
       </c>
       <c r="M96">
-        <v>184.1484816</v>
+        <v>186.107508</v>
       </c>
       <c r="N96">
-        <v>-122.7484816</v>
+        <v>-124.707508</v>
       </c>
       <c r="O96">
-        <v>-27.004665952</v>
+        <v>-27.43565176</v>
       </c>
       <c r="P96">
-        <v>-95.74381564800001</v>
+        <v>-97.27185624000002</v>
       </c>
       <c r="Q96">
-        <v>-86.24381564800001</v>
+        <v>-87.77185624000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8513775149705055</v>
+        <v>1.012493017964607</v>
       </c>
       <c r="T96">
-        <v>10.49937555874687</v>
+        <v>12.59925067049625</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07335384947317425</v>
+        <v>0.0725817036892461</v>
       </c>
       <c r="W96">
-        <v>0.2185031622942255</v>
+        <v>0.2186852342700758</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3334265885144284</v>
+        <v>0.3299168349511187</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9306,22 +9306,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2583756234548023</v>
+        <v>0.2602756234548023</v>
       </c>
       <c r="C97">
-        <v>-562.5838266466841</v>
+        <v>-572.6359163634818</v>
       </c>
       <c r="D97">
-        <v>196.876173353316</v>
+        <v>195.1320836365183</v>
       </c>
       <c r="E97">
-        <v>679.1600000000001</v>
+        <v>687.4680000000001</v>
       </c>
       <c r="F97">
-        <v>789.2600000000001</v>
+        <v>797.5680000000001</v>
       </c>
       <c r="G97">
         <v>29.8</v>
@@ -9342,37 +9342,37 @@
         <v>61.4</v>
       </c>
       <c r="M97">
-        <v>186.107508</v>
+        <v>188.0665344</v>
       </c>
       <c r="N97">
-        <v>-124.707508</v>
+        <v>-126.6665344</v>
       </c>
       <c r="O97">
-        <v>-27.43565176</v>
+        <v>-27.86663756800001</v>
       </c>
       <c r="P97">
-        <v>-97.27185624000002</v>
+        <v>-98.79989683200002</v>
       </c>
       <c r="Q97">
-        <v>-87.77185624000001</v>
+        <v>-89.299896832</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.012493017964607</v>
+        <v>1.25416627245576</v>
       </c>
       <c r="T97">
-        <v>12.59925067049625</v>
+        <v>15.74906333812032</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0725817036892461</v>
+        <v>0.07182564427581645</v>
       </c>
       <c r="W97">
-        <v>0.2186852342700758</v>
+        <v>0.2188635130797625</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3299168349511187</v>
+        <v>0.3264802012537111</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9388,22 +9388,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2602756234548023</v>
+        <v>0.2621756234548023</v>
       </c>
       <c r="C98">
-        <v>-572.6359163634817</v>
+        <v>-582.6573762855826</v>
       </c>
       <c r="D98">
-        <v>195.1320836365183</v>
+        <v>193.4186237144175</v>
       </c>
       <c r="E98">
-        <v>687.468</v>
+        <v>695.7760000000001</v>
       </c>
       <c r="F98">
-        <v>797.568</v>
+        <v>805.8760000000001</v>
       </c>
       <c r="G98">
         <v>29.8</v>
@@ -9424,37 +9424,37 @@
         <v>61.4</v>
       </c>
       <c r="M98">
-        <v>188.0665344</v>
+        <v>190.0255608</v>
       </c>
       <c r="N98">
-        <v>-126.6665344</v>
+        <v>-128.6255608</v>
       </c>
       <c r="O98">
-        <v>-27.866637568</v>
+        <v>-28.297623376</v>
       </c>
       <c r="P98">
-        <v>-98.79989683199999</v>
+        <v>-100.327937424</v>
       </c>
       <c r="Q98">
-        <v>-89.29989683199997</v>
+        <v>-90.827937424</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.254166272455756</v>
+        <v>1.656955029941009</v>
       </c>
       <c r="T98">
-        <v>15.74906333812027</v>
+        <v>20.9987511174937</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07182564427581646</v>
+        <v>0.07108517371627196</v>
       </c>
       <c r="W98">
-        <v>0.2188635130797625</v>
+        <v>0.2190381160377031</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3264802012537112</v>
+        <v>0.3231144259830544</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9470,22 +9470,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2621756234548023</v>
+        <v>0.2640756234548023</v>
       </c>
       <c r="C99">
-        <v>-582.6573762855826</v>
+        <v>-592.6490062724807</v>
       </c>
       <c r="D99">
-        <v>193.4186237144175</v>
+        <v>191.7349937275193</v>
       </c>
       <c r="E99">
-        <v>695.7760000000001</v>
+        <v>704.0840000000001</v>
       </c>
       <c r="F99">
-        <v>805.8760000000001</v>
+        <v>814.1840000000001</v>
       </c>
       <c r="G99">
         <v>29.8</v>
@@ -9506,37 +9506,37 @@
         <v>61.4</v>
       </c>
       <c r="M99">
-        <v>190.0255608</v>
+        <v>191.9845872</v>
       </c>
       <c r="N99">
-        <v>-128.6255608</v>
+        <v>-130.5845872</v>
       </c>
       <c r="O99">
-        <v>-28.297623376</v>
+        <v>-28.728609184</v>
       </c>
       <c r="P99">
-        <v>-100.327937424</v>
+        <v>-101.855978016</v>
       </c>
       <c r="Q99">
-        <v>-90.827937424</v>
+        <v>-92.35597801599999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.656955029941009</v>
+        <v>2.462532544911512</v>
       </c>
       <c r="T99">
-        <v>20.9987511174937</v>
+        <v>31.49812667624055</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07108517371627196</v>
+        <v>0.07035981480079979</v>
       </c>
       <c r="W99">
-        <v>0.2190381160377031</v>
+        <v>0.2192091556699714</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3231144259830544</v>
+        <v>0.3198173400036355</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9552,22 +9552,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2640756234548023</v>
+        <v>0.2659756234548023</v>
       </c>
       <c r="C100">
-        <v>-592.6490062724807</v>
+        <v>-602.611578574201</v>
       </c>
       <c r="D100">
-        <v>191.7349937275193</v>
+        <v>190.0804214257991</v>
       </c>
       <c r="E100">
-        <v>704.0840000000001</v>
+        <v>712.3920000000001</v>
       </c>
       <c r="F100">
-        <v>814.1840000000001</v>
+        <v>822.4920000000001</v>
       </c>
       <c r="G100">
         <v>29.8</v>
@@ -9588,37 +9588,37 @@
         <v>61.4</v>
       </c>
       <c r="M100">
-        <v>191.9845872</v>
+        <v>193.9436136</v>
       </c>
       <c r="N100">
-        <v>-130.5845872</v>
+        <v>-132.5436136</v>
       </c>
       <c r="O100">
-        <v>-28.728609184</v>
+        <v>-29.159594992</v>
       </c>
       <c r="P100">
-        <v>-101.855978016</v>
+        <v>-103.384018608</v>
       </c>
       <c r="Q100">
-        <v>-92.35597801599999</v>
+        <v>-93.88401860800002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.462532544911512</v>
+        <v>4.879265089823025</v>
       </c>
       <c r="T100">
-        <v>31.49812667624055</v>
+        <v>62.9962533524811</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07035981480079979</v>
+        <v>0.06964910960079172</v>
       </c>
       <c r="W100">
-        <v>0.2192091556699714</v>
+        <v>0.2193767399561333</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9626,91 +9626,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3198173400036355</v>
+        <v>0.3165868618217805</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2659756234548023</v>
-      </c>
-      <c r="C101">
-        <v>-602.611578574201</v>
-      </c>
-      <c r="D101">
-        <v>190.0804214257991</v>
-      </c>
-      <c r="E101">
-        <v>712.3920000000001</v>
-      </c>
-      <c r="F101">
-        <v>822.4920000000001</v>
-      </c>
-      <c r="G101">
-        <v>29.8</v>
-      </c>
-      <c r="H101">
-        <v>720.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="K101">
-        <v>9.500000000000007</v>
-      </c>
-      <c r="L101">
-        <v>61.4</v>
-      </c>
-      <c r="M101">
-        <v>193.9436136</v>
-      </c>
-      <c r="N101">
-        <v>-132.5436136</v>
-      </c>
-      <c r="O101">
-        <v>-29.159594992</v>
-      </c>
-      <c r="P101">
-        <v>-103.384018608</v>
-      </c>
-      <c r="Q101">
-        <v>-93.88401860800002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.879265089823025</v>
-      </c>
-      <c r="T101">
-        <v>62.9962533524811</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06964910960079172</v>
-      </c>
-      <c r="W101">
-        <v>0.2193767399561333</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3165868618217805</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
